--- a/outputs/44296.xlsx
+++ b/outputs/44296.xlsx
@@ -282,16 +282,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -547,1363 +551,1363 @@
   <dimension ref="B1:R53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="3" style="0" width="9"/>
+    <col collapsed="false" customWidth="false" hidden="true" outlineLevel="0" max="10" min="3" style="1" width="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="0" t="n">
-        <v>2015</v>
-      </c>
-      <c r="M1" s="0" t="n">
-        <v>2016</v>
-      </c>
-      <c r="N1" s="0" t="n">
+      <c r="L1" s="1" t="n">
+        <v>2015</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <v>2016</v>
+      </c>
+      <c r="N1" s="1" t="n">
         <v>2017</v>
       </c>
-      <c r="O1" s="0" t="n">
+      <c r="O1" s="1" t="n">
         <v>2018</v>
       </c>
-      <c r="P1" s="0" t="n">
+      <c r="P1" s="1" t="n">
         <v>2019</v>
       </c>
-      <c r="Q1" s="0" t="n">
+      <c r="Q1" s="1" t="n">
         <v>2020</v>
       </c>
-      <c r="R1" s="0" t="n">
+      <c r="R1" s="1" t="n">
         <v>2021</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="0" t="n">
+      <c r="L3" s="1" t="n">
         <v>0.977263720980125</v>
       </c>
-      <c r="M3" s="0" t="n">
+      <c r="M3" s="1" t="n">
         <v>0.369694550249851</v>
       </c>
-      <c r="N3" s="0" t="n">
+      <c r="N3" s="1" t="n">
         <v>0.582186273342648</v>
       </c>
-      <c r="O3" s="0" t="n">
+      <c r="O3" s="1" t="n">
         <v>0.34777775622301</v>
       </c>
-      <c r="P3" s="0" t="n">
+      <c r="P3" s="1" t="n">
         <v>0.372438970314569</v>
       </c>
-      <c r="Q3" s="0" t="n">
+      <c r="Q3" s="1" t="n">
         <v>0.643300783126722</v>
       </c>
-      <c r="R3" s="0" t="n">
+      <c r="R3" s="1" t="n">
         <v>0.260453523948227</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="0" t="n">
+      <c r="L4" s="1" t="n">
         <v>0.942556599505759</v>
       </c>
-      <c r="M4" s="0" t="n">
+      <c r="M4" s="1" t="n">
         <v>0.718165777391587</v>
       </c>
-      <c r="N4" s="0" t="n">
+      <c r="N4" s="1" t="n">
         <v>0.0834587161985507</v>
       </c>
-      <c r="O4" s="0" t="n">
+      <c r="O4" s="1" t="n">
         <v>0.931598750653575</v>
       </c>
-      <c r="P4" s="0" t="n">
+      <c r="P4" s="1" t="n">
         <v>0.478821856070859</v>
       </c>
-      <c r="Q4" s="0" t="n">
+      <c r="Q4" s="1" t="n">
         <v>0.109798767617252</v>
       </c>
-      <c r="R4" s="0" t="n">
+      <c r="R4" s="1" t="n">
         <v>0.14106254530949</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L5" s="0" t="n">
+      <c r="L5" s="1" t="n">
         <v>0.12448902388882</v>
       </c>
-      <c r="M5" s="0" t="n">
+      <c r="M5" s="1" t="n">
         <v>0.647574861591199</v>
       </c>
-      <c r="N5" s="0" t="n">
+      <c r="N5" s="1" t="n">
         <v>0.987161398583055</v>
       </c>
-      <c r="O5" s="0" t="n">
+      <c r="O5" s="1" t="n">
         <v>0.947105215513877</v>
       </c>
-      <c r="P5" s="0" t="n">
+      <c r="P5" s="1" t="n">
         <v>0.121861441758323</v>
       </c>
-      <c r="Q5" s="0" t="n">
+      <c r="Q5" s="1" t="n">
         <v>0.369007190393768</v>
       </c>
-      <c r="R5" s="0" t="n">
+      <c r="R5" s="1" t="n">
         <v>0.824481150492699</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="0" t="n">
+      <c r="L6" s="1" t="n">
         <v>0.718263105033681</v>
       </c>
-      <c r="M6" s="0" t="n">
+      <c r="M6" s="1" t="n">
         <v>0.918250677089609</v>
       </c>
-      <c r="N6" s="0" t="n">
+      <c r="N6" s="1" t="n">
         <v>0.421904845868603</v>
       </c>
-      <c r="O6" s="0" t="n">
+      <c r="O6" s="1" t="n">
         <v>0.493597613524291</v>
       </c>
-      <c r="P6" s="0" t="n">
+      <c r="P6" s="1" t="n">
         <v>0.0296310454977874</v>
       </c>
-      <c r="Q6" s="0" t="n">
+      <c r="Q6" s="1" t="n">
         <v>0.7770534829439</v>
       </c>
-      <c r="R6" s="0" t="n">
+      <c r="R6" s="1" t="n">
         <v>0.363025664981948</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="0" t="n">
+      <c r="L7" s="1" t="n">
         <v>0.676907924564291</v>
       </c>
-      <c r="M7" s="0" t="n">
+      <c r="M7" s="1" t="n">
         <v>0.470295046817084</v>
       </c>
-      <c r="N7" s="0" t="n">
+      <c r="N7" s="1" t="n">
         <v>0.00341186720391529</v>
       </c>
-      <c r="O7" s="0" t="n">
+      <c r="O7" s="1" t="n">
         <v>0.818726627881423</v>
       </c>
-      <c r="P7" s="0" t="n">
+      <c r="P7" s="1" t="n">
         <v>0.396613724721413</v>
       </c>
-      <c r="Q7" s="0" t="n">
+      <c r="Q7" s="1" t="n">
         <v>0.870993009592726</v>
       </c>
-      <c r="R7" s="0" t="n">
+      <c r="R7" s="1" t="n">
         <v>0.447704907494144</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="0" t="n">
+      <c r="L8" s="1" t="n">
         <v>0.287396920270059</v>
       </c>
-      <c r="M8" s="0" t="n">
+      <c r="M8" s="1" t="n">
         <v>0.56978655216477</v>
       </c>
-      <c r="N8" s="0" t="n">
+      <c r="N8" s="1" t="n">
         <v>0.213582172049471</v>
       </c>
-      <c r="O8" s="0" t="n">
+      <c r="O8" s="1" t="n">
         <v>0.339160545154279</v>
       </c>
-      <c r="P8" s="0" t="n">
+      <c r="P8" s="1" t="n">
         <v>0.334326994551706</v>
       </c>
-      <c r="Q8" s="0" t="n">
+      <c r="Q8" s="1" t="n">
         <v>0.350418190160173</v>
       </c>
-      <c r="R8" s="0" t="n">
+      <c r="R8" s="1" t="n">
         <v>0.241931405599991</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="0" t="n">
+      <c r="L9" s="1" t="n">
         <v>0.0920880379017474</v>
       </c>
-      <c r="M9" s="0" t="n">
+      <c r="M9" s="1" t="n">
         <v>0.314761212646374</v>
       </c>
-      <c r="N9" s="0" t="n">
+      <c r="N9" s="1" t="n">
         <v>0.0152260561731484</v>
       </c>
-      <c r="O9" s="0" t="n">
+      <c r="O9" s="1" t="n">
         <v>0.265617556402024</v>
       </c>
-      <c r="P9" s="0" t="n">
+      <c r="P9" s="1" t="n">
         <v>0.0474966394804325</v>
       </c>
-      <c r="Q9" s="0" t="n">
+      <c r="Q9" s="1" t="n">
         <v>0.441405538093706</v>
       </c>
-      <c r="R9" s="0" t="n">
+      <c r="R9" s="1" t="n">
         <v>0.623141542768211</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L10" s="0" t="n">
+      <c r="L10" s="1" t="n">
         <v>0.43894251611377</v>
       </c>
-      <c r="M10" s="0" t="n">
+      <c r="M10" s="1" t="n">
         <v>0.619263449452447</v>
       </c>
-      <c r="N10" s="0" t="n">
+      <c r="N10" s="1" t="n">
         <v>0.948369053305246</v>
       </c>
-      <c r="O10" s="0" t="n">
+      <c r="O10" s="1" t="n">
         <v>0.91959611389121</v>
       </c>
-      <c r="P10" s="0" t="n">
+      <c r="P10" s="1" t="n">
         <v>0.78572964427287</v>
       </c>
-      <c r="Q10" s="0" t="n">
+      <c r="Q10" s="1" t="n">
         <v>0.672898212902939</v>
       </c>
-      <c r="R10" s="0" t="n">
+      <c r="R10" s="1" t="n">
         <v>0.49648873455372</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="0" t="n">
+      <c r="L11" s="1" t="n">
         <v>0.346262636077046</v>
       </c>
-      <c r="M11" s="0" t="n">
+      <c r="M11" s="1" t="n">
         <v>0.422234596278344</v>
       </c>
-      <c r="N11" s="0" t="n">
+      <c r="N11" s="1" t="n">
         <v>0.213553474941292</v>
       </c>
-      <c r="O11" s="0" t="n">
+      <c r="O11" s="1" t="n">
         <v>0.405984480003696</v>
       </c>
-      <c r="P11" s="0" t="n">
+      <c r="P11" s="1" t="n">
         <v>0.441460785942547</v>
       </c>
-      <c r="Q11" s="0" t="n">
+      <c r="Q11" s="1" t="n">
         <v>0.0697450101616706</v>
       </c>
-      <c r="R11" s="0" t="n">
+      <c r="R11" s="1" t="n">
         <v>0.311460779257717</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="0" t="n">
+      <c r="L12" s="1" t="n">
         <v>0.606937263920749</v>
       </c>
-      <c r="M12" s="0" t="n">
+      <c r="M12" s="1" t="n">
         <v>0.110630909969275</v>
       </c>
-      <c r="N12" s="0" t="n">
+      <c r="N12" s="1" t="n">
         <v>0.307616409576699</v>
       </c>
-      <c r="O12" s="0" t="n">
+      <c r="O12" s="1" t="n">
         <v>0.711995598511812</v>
       </c>
-      <c r="P12" s="0" t="n">
+      <c r="P12" s="1" t="n">
         <v>0.325891771931479</v>
       </c>
-      <c r="Q12" s="0" t="n">
+      <c r="Q12" s="1" t="n">
         <v>0.922242845663515</v>
       </c>
-      <c r="R12" s="0" t="n">
+      <c r="R12" s="1" t="n">
         <v>0.989221272582127</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L13" s="0" t="n">
+      <c r="L13" s="1" t="n">
         <v>0.208578383160297</v>
       </c>
-      <c r="M13" s="0" t="n">
+      <c r="M13" s="1" t="n">
         <v>0.504589039555236</v>
       </c>
-      <c r="N13" s="0" t="n">
+      <c r="N13" s="1" t="n">
         <v>0.449460693893583</v>
       </c>
-      <c r="O13" s="0" t="n">
+      <c r="O13" s="1" t="n">
         <v>0.96282156395357</v>
       </c>
-      <c r="P13" s="0" t="n">
+      <c r="P13" s="1" t="n">
         <v>0.205896097140467</v>
       </c>
-      <c r="Q13" s="0" t="n">
+      <c r="Q13" s="1" t="n">
         <v>0.444922423891527</v>
       </c>
-      <c r="R13" s="0" t="n">
+      <c r="R13" s="1" t="n">
         <v>0.264134871093357</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="L14" s="0" t="n">
+      <c r="L14" s="1" t="n">
         <v>0.832246441364454</v>
       </c>
-      <c r="M14" s="0" t="n">
+      <c r="M14" s="1" t="n">
         <v>0.561936675559634</v>
       </c>
-      <c r="N14" s="0" t="n">
+      <c r="N14" s="1" t="n">
         <v>0.784404271834524</v>
       </c>
-      <c r="O14" s="0" t="n">
+      <c r="O14" s="1" t="n">
         <v>0.327598983015279</v>
       </c>
-      <c r="P14" s="0" t="n">
+      <c r="P14" s="1" t="n">
         <v>0.878466495590608</v>
       </c>
-      <c r="Q14" s="0" t="n">
+      <c r="Q14" s="1" t="n">
         <v>0.0650100860207771</v>
       </c>
-      <c r="R14" s="0" t="n">
+      <c r="R14" s="1" t="n">
         <v>0.687012246593567</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L15" s="0" t="n">
+      <c r="L15" s="1" t="n">
         <v>0.815765208709144</v>
       </c>
-      <c r="M15" s="0" t="n">
+      <c r="M15" s="1" t="n">
         <v>0.0121997857164132</v>
       </c>
-      <c r="N15" s="0" t="n">
+      <c r="N15" s="1" t="n">
         <v>0.706241724410266</v>
       </c>
-      <c r="O15" s="0" t="n">
+      <c r="O15" s="1" t="n">
         <v>0.259839980551131</v>
       </c>
-      <c r="P15" s="0" t="n">
+      <c r="P15" s="1" t="n">
         <v>0.376126882450468</v>
       </c>
-      <c r="Q15" s="0" t="n">
+      <c r="Q15" s="1" t="n">
         <v>0.331174320374142</v>
       </c>
-      <c r="R15" s="0" t="n">
+      <c r="R15" s="1" t="n">
         <v>0.886412883390327</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L16" s="0" t="n">
+      <c r="L16" s="1" t="n">
         <v>0.984343202798317</v>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="M16" s="1" t="n">
         <v>0.0744918816064607</v>
       </c>
-      <c r="N16" s="0" t="n">
+      <c r="N16" s="1" t="n">
         <v>0.822101942281418</v>
       </c>
-      <c r="O16" s="0" t="n">
+      <c r="O16" s="1" t="n">
         <v>0.100645585341044</v>
       </c>
-      <c r="P16" s="0" t="n">
+      <c r="P16" s="1" t="n">
         <v>0.522204109442168</v>
       </c>
-      <c r="Q16" s="0" t="n">
+      <c r="Q16" s="1" t="n">
         <v>0.413552327612029</v>
       </c>
-      <c r="R16" s="0" t="n">
+      <c r="R16" s="1" t="n">
         <v>0.710010133798841</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="0" t="n">
+      <c r="L17" s="1" t="n">
         <v>0.589511751085022</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M17" s="1" t="n">
         <v>0.101270170745148</v>
       </c>
-      <c r="N17" s="0" t="n">
+      <c r="N17" s="1" t="n">
         <v>0.618892138987211</v>
       </c>
-      <c r="O17" s="0" t="n">
+      <c r="O17" s="1" t="n">
         <v>0.922323426241092</v>
       </c>
-      <c r="P17" s="0" t="n">
+      <c r="P17" s="1" t="n">
         <v>0.907577241611958</v>
       </c>
-      <c r="Q17" s="0" t="n">
+      <c r="Q17" s="1" t="n">
         <v>0.333554760070393</v>
       </c>
-      <c r="R17" s="0" t="n">
+      <c r="R17" s="1" t="n">
         <v>0.844741368821292</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L18" s="0" t="n">
+      <c r="L18" s="1" t="n">
         <v>0.934109273163392</v>
       </c>
-      <c r="M18" s="0" t="n">
+      <c r="M18" s="1" t="n">
         <v>0.444939584993711</v>
       </c>
-      <c r="N18" s="0" t="n">
+      <c r="N18" s="1" t="n">
         <v>0.500283335592544</v>
       </c>
-      <c r="O18" s="0" t="n">
+      <c r="O18" s="1" t="n">
         <v>0.0389117081496069</v>
       </c>
-      <c r="P18" s="0" t="n">
+      <c r="P18" s="1" t="n">
         <v>0.739395364990323</v>
       </c>
-      <c r="Q18" s="0" t="n">
+      <c r="Q18" s="1" t="n">
         <v>0.634944320591584</v>
       </c>
-      <c r="R18" s="0" t="n">
+      <c r="R18" s="1" t="n">
         <v>0.186388853701022</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L19" s="0" t="n">
+      <c r="L19" s="1" t="n">
         <v>0.111624290674215</v>
       </c>
-      <c r="M19" s="0" t="n">
+      <c r="M19" s="1" t="n">
         <v>0.813128951408209</v>
       </c>
-      <c r="N19" s="0" t="n">
+      <c r="N19" s="1" t="n">
         <v>0.560209819355917</v>
       </c>
-      <c r="O19" s="0" t="n">
+      <c r="O19" s="1" t="n">
         <v>0.738421607156787</v>
       </c>
-      <c r="P19" s="0" t="n">
+      <c r="P19" s="1" t="n">
         <v>0.308459068133962</v>
       </c>
-      <c r="Q19" s="0" t="n">
+      <c r="Q19" s="1" t="n">
         <v>0.762729118761859</v>
       </c>
-      <c r="R19" s="0" t="n">
+      <c r="R19" s="1" t="n">
         <v>0.748440557191403</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L20" s="0" t="n">
+      <c r="L20" s="1" t="n">
         <v>0.310555350830881</v>
       </c>
-      <c r="M20" s="0" t="n">
+      <c r="M20" s="1" t="n">
         <v>0.833368049338167</v>
       </c>
-      <c r="N20" s="0" t="n">
+      <c r="N20" s="1" t="n">
         <v>0.488999059951372</v>
       </c>
-      <c r="O20" s="0" t="n">
+      <c r="O20" s="1" t="n">
         <v>0.338042487075699</v>
       </c>
-      <c r="P20" s="0" t="n">
+      <c r="P20" s="1" t="n">
         <v>0.485036860149675</v>
       </c>
-      <c r="Q20" s="0" t="n">
+      <c r="Q20" s="1" t="n">
         <v>0.524112327012119</v>
       </c>
-      <c r="R20" s="0" t="n">
+      <c r="R20" s="1" t="n">
         <v>0.311897813463102</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L21" s="0" t="n">
+      <c r="L21" s="1" t="n">
         <v>0.081325519667791</v>
       </c>
-      <c r="M21" s="0" t="n">
+      <c r="M21" s="1" t="n">
         <v>0.980309702492869</v>
       </c>
-      <c r="N21" s="0" t="n">
+      <c r="N21" s="1" t="n">
         <v>0.829908680295095</v>
       </c>
-      <c r="O21" s="0" t="n">
+      <c r="O21" s="1" t="n">
         <v>0.827108594237288</v>
       </c>
-      <c r="P21" s="0" t="n">
+      <c r="P21" s="1" t="n">
         <v>0.169269571223571</v>
       </c>
-      <c r="Q21" s="0" t="n">
+      <c r="Q21" s="1" t="n">
         <v>0.175439294302267</v>
       </c>
-      <c r="R21" s="0" t="n">
+      <c r="R21" s="1" t="n">
         <v>0.720572351582371</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L22" s="0" t="n">
+      <c r="L22" s="1" t="n">
         <v>0.460078181606601</v>
       </c>
-      <c r="M22" s="0" t="n">
+      <c r="M22" s="1" t="n">
         <v>0.167787479706479</v>
       </c>
-      <c r="N22" s="0" t="n">
+      <c r="N22" s="1" t="n">
         <v>0.647430850436138</v>
       </c>
-      <c r="O22" s="0" t="n">
+      <c r="O22" s="1" t="n">
         <v>0.922445772110018</v>
       </c>
-      <c r="P22" s="0" t="n">
+      <c r="P22" s="1" t="n">
         <v>0.895988999238945</v>
       </c>
-      <c r="Q22" s="0" t="n">
+      <c r="Q22" s="1" t="n">
         <v>0.533851949942619</v>
       </c>
-      <c r="R22" s="0" t="n">
+      <c r="R22" s="1" t="n">
         <v>0.420424468768885</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L23" s="0" t="n">
+      <c r="L23" s="1" t="n">
         <v>0.922944198286225</v>
       </c>
-      <c r="M23" s="0" t="n">
+      <c r="M23" s="1" t="n">
         <v>0.745094760504618</v>
       </c>
-      <c r="N23" s="0" t="n">
+      <c r="N23" s="1" t="n">
         <v>0.131996752620993</v>
       </c>
-      <c r="O23" s="0" t="n">
+      <c r="O23" s="1" t="n">
         <v>0.980707256616181</v>
       </c>
-      <c r="P23" s="0" t="n">
+      <c r="P23" s="1" t="n">
         <v>0.347588925378165</v>
       </c>
-      <c r="Q23" s="0" t="n">
+      <c r="Q23" s="1" t="n">
         <v>0.15963962100282</v>
       </c>
-      <c r="R23" s="0" t="n">
+      <c r="R23" s="1" t="n">
         <v>0.957503610230947</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L24" s="0" t="n">
+      <c r="L24" s="1" t="n">
         <v>0.293275438338128</v>
       </c>
-      <c r="M24" s="0" t="n">
+      <c r="M24" s="1" t="n">
         <v>0.392068209481472</v>
       </c>
-      <c r="N24" s="0" t="n">
+      <c r="N24" s="1" t="n">
         <v>0.478405033986869</v>
       </c>
-      <c r="O24" s="0" t="n">
+      <c r="O24" s="1" t="n">
         <v>0.464168706359762</v>
       </c>
-      <c r="P24" s="0" t="n">
+      <c r="P24" s="1" t="n">
         <v>0.974221751434389</v>
       </c>
-      <c r="Q24" s="0" t="n">
+      <c r="Q24" s="1" t="n">
         <v>0.180866386002721</v>
       </c>
-      <c r="R24" s="0" t="n">
+      <c r="R24" s="1" t="n">
         <v>0.280076139177321</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L25" s="0" t="n">
+      <c r="L25" s="1" t="n">
         <v>0.151646652406461</v>
       </c>
-      <c r="M25" s="0" t="n">
+      <c r="M25" s="1" t="n">
         <v>0.404066649594268</v>
       </c>
-      <c r="N25" s="0" t="n">
+      <c r="N25" s="1" t="n">
         <v>0.845171276225484</v>
       </c>
-      <c r="O25" s="0" t="n">
+      <c r="O25" s="1" t="n">
         <v>0.243414987546066</v>
       </c>
-      <c r="P25" s="0" t="n">
+      <c r="P25" s="1" t="n">
         <v>0.643583580529968</v>
       </c>
-      <c r="Q25" s="0" t="n">
+      <c r="Q25" s="1" t="n">
         <v>0.855309961555194</v>
       </c>
-      <c r="R25" s="0" t="n">
+      <c r="R25" s="1" t="n">
         <v>0.801947336315541</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="L26" s="0" t="n">
+      <c r="L26" s="1" t="n">
         <v>0.483752214444178</v>
       </c>
-      <c r="M26" s="0" t="n">
+      <c r="M26" s="1" t="n">
         <v>0.962098177585588</v>
       </c>
-      <c r="N26" s="0" t="n">
+      <c r="N26" s="1" t="n">
         <v>0.607387658284745</v>
       </c>
-      <c r="O26" s="0" t="n">
+      <c r="O26" s="1" t="n">
         <v>0.227311710818299</v>
       </c>
-      <c r="P26" s="0" t="n">
+      <c r="P26" s="1" t="n">
         <v>0.891795744842292</v>
       </c>
-      <c r="Q26" s="0" t="n">
+      <c r="Q26" s="1" t="n">
         <v>0.991630813588724</v>
       </c>
-      <c r="R26" s="0" t="n">
+      <c r="R26" s="1" t="n">
         <v>0.290333851887237</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L27" s="0" t="n">
+      <c r="L27" s="1" t="n">
         <v>0.202779968226557</v>
       </c>
-      <c r="M27" s="0" t="n">
+      <c r="M27" s="1" t="n">
         <v>0.0463131954792417</v>
       </c>
-      <c r="N27" s="0" t="n">
+      <c r="N27" s="1" t="n">
         <v>0.636099666901789</v>
       </c>
-      <c r="O27" s="0" t="n">
+      <c r="O27" s="1" t="n">
         <v>0.337658138602834</v>
       </c>
-      <c r="P27" s="0" t="n">
+      <c r="P27" s="1" t="n">
         <v>0.719988044146216</v>
       </c>
-      <c r="Q27" s="0" t="n">
+      <c r="Q27" s="1" t="n">
         <v>0.224421532721235</v>
       </c>
-      <c r="R27" s="0" t="n">
+      <c r="R27" s="1" t="n">
         <v>0.728976326090558</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L28" s="0" t="n">
+      <c r="L28" s="1" t="n">
         <v>0.550544014823825</v>
       </c>
-      <c r="M28" s="0" t="n">
+      <c r="M28" s="1" t="n">
         <v>0.987397660151677</v>
       </c>
-      <c r="N28" s="0" t="n">
+      <c r="N28" s="1" t="n">
         <v>0.527483419094511</v>
       </c>
-      <c r="O28" s="0" t="n">
+      <c r="O28" s="1" t="n">
         <v>0.290937923712584</v>
       </c>
-      <c r="P28" s="0" t="n">
+      <c r="P28" s="1" t="n">
         <v>0.587126936781088</v>
       </c>
-      <c r="Q28" s="0" t="n">
+      <c r="Q28" s="1" t="n">
         <v>0.0987279284394804</v>
       </c>
-      <c r="R28" s="0" t="n">
+      <c r="R28" s="1" t="n">
         <v>0.696759183500475</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="L29" s="0" t="n">
+      <c r="L29" s="1" t="n">
         <v>0.890567115157197</v>
       </c>
-      <c r="M29" s="0" t="n">
+      <c r="M29" s="1" t="n">
         <v>0.434370975072386</v>
       </c>
-      <c r="N29" s="0" t="n">
+      <c r="N29" s="1" t="n">
         <v>0.294407829085472</v>
       </c>
-      <c r="O29" s="0" t="n">
+      <c r="O29" s="1" t="n">
         <v>0.110684502377711</v>
       </c>
-      <c r="P29" s="0" t="n">
+      <c r="P29" s="1" t="n">
         <v>0.134777770614773</v>
       </c>
-      <c r="Q29" s="0" t="n">
+      <c r="Q29" s="1" t="n">
         <v>0.832272452208398</v>
       </c>
-      <c r="R29" s="0" t="n">
+      <c r="R29" s="1" t="n">
         <v>0.649671154595366</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L30" s="0" t="n">
+      <c r="L30" s="1" t="n">
         <v>0.202300147891679</v>
       </c>
-      <c r="M30" s="0" t="n">
+      <c r="M30" s="1" t="n">
         <v>0.778758181214608</v>
       </c>
-      <c r="N30" s="0" t="n">
+      <c r="N30" s="1" t="n">
         <v>0.675165587212274</v>
       </c>
-      <c r="O30" s="0" t="n">
+      <c r="O30" s="1" t="n">
         <v>0.597313513766991</v>
       </c>
-      <c r="P30" s="0" t="n">
+      <c r="P30" s="1" t="n">
         <v>0.273201626043764</v>
       </c>
-      <c r="Q30" s="0" t="n">
+      <c r="Q30" s="1" t="n">
         <v>0.902400718323221</v>
       </c>
-      <c r="R30" s="0" t="n">
+      <c r="R30" s="1" t="n">
         <v>0.718667090472212</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L31" s="0" t="n">
+      <c r="L31" s="1" t="n">
         <v>0.00735575830023227</v>
       </c>
-      <c r="M31" s="0" t="n">
+      <c r="M31" s="1" t="n">
         <v>0.997040199373517</v>
       </c>
-      <c r="N31" s="0" t="n">
+      <c r="N31" s="1" t="n">
         <v>0.944887394884915</v>
       </c>
-      <c r="O31" s="0" t="n">
+      <c r="O31" s="1" t="n">
         <v>0.516646270539833</v>
       </c>
-      <c r="P31" s="0" t="n">
+      <c r="P31" s="1" t="n">
         <v>0.214138996422755</v>
       </c>
-      <c r="Q31" s="0" t="n">
+      <c r="Q31" s="1" t="n">
         <v>0.811399632472324</v>
       </c>
-      <c r="R31" s="0" t="n">
+      <c r="R31" s="1" t="n">
         <v>0.757276104244038</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L32" s="0" t="n">
+      <c r="L32" s="1" t="n">
         <v>0.496075380477184</v>
       </c>
-      <c r="M32" s="0" t="n">
+      <c r="M32" s="1" t="n">
         <v>0.546003573654997</v>
       </c>
-      <c r="N32" s="0" t="n">
+      <c r="N32" s="1" t="n">
         <v>0.201889070806022</v>
       </c>
-      <c r="O32" s="0" t="n">
+      <c r="O32" s="1" t="n">
         <v>0.640778967586947</v>
       </c>
-      <c r="P32" s="0" t="n">
+      <c r="P32" s="1" t="n">
         <v>0.957564576027983</v>
       </c>
-      <c r="Q32" s="0" t="n">
+      <c r="Q32" s="1" t="n">
         <v>0.0383091285274511</v>
       </c>
-      <c r="R32" s="0" t="n">
+      <c r="R32" s="1" t="n">
         <v>0.596202180113099</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L33" s="0" t="n">
+      <c r="L33" s="1" t="n">
         <v>0.558832213932223</v>
       </c>
-      <c r="M33" s="0" t="n">
+      <c r="M33" s="1" t="n">
         <v>0.0958252934572622</v>
       </c>
-      <c r="N33" s="0" t="n">
+      <c r="N33" s="1" t="n">
         <v>0.142261015108602</v>
       </c>
-      <c r="O33" s="0" t="n">
+      <c r="O33" s="1" t="n">
         <v>0.743663193903362</v>
       </c>
-      <c r="P33" s="0" t="n">
+      <c r="P33" s="1" t="n">
         <v>0.959810983314647</v>
       </c>
-      <c r="Q33" s="0" t="n">
+      <c r="Q33" s="1" t="n">
         <v>0.754139361324187</v>
       </c>
-      <c r="R33" s="0" t="n">
+      <c r="R33" s="1" t="n">
         <v>0.491010038826128</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L34" s="0" t="n">
+      <c r="L34" s="1" t="n">
         <v>0.0428436978656417</v>
       </c>
-      <c r="M34" s="0" t="n">
+      <c r="M34" s="1" t="n">
         <v>0.165230235461094</v>
       </c>
-      <c r="N34" s="0" t="n">
+      <c r="N34" s="1" t="n">
         <v>0.493468134858165</v>
       </c>
-      <c r="O34" s="0" t="n">
+      <c r="O34" s="1" t="n">
         <v>0.283480626482824</v>
       </c>
-      <c r="P34" s="0" t="n">
+      <c r="P34" s="1" t="n">
         <v>0.957943138232913</v>
       </c>
-      <c r="Q34" s="0" t="n">
+      <c r="Q34" s="1" t="n">
         <v>0.13475424815334</v>
       </c>
-      <c r="R34" s="0" t="n">
+      <c r="R34" s="1" t="n">
         <v>0.412004653529979</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="0" t="n">
+      <c r="L35" s="1" t="n">
         <v>0.882410020278209</v>
       </c>
-      <c r="M35" s="0" t="n">
+      <c r="M35" s="1" t="n">
         <v>0.607227175985319</v>
       </c>
-      <c r="N35" s="0" t="n">
+      <c r="N35" s="1" t="n">
         <v>0.795793238585232</v>
       </c>
-      <c r="O35" s="0" t="n">
+      <c r="O35" s="1" t="n">
         <v>0.377237731148291</v>
       </c>
-      <c r="P35" s="0" t="n">
+      <c r="P35" s="1" t="n">
         <v>0.488519626865039</v>
       </c>
-      <c r="Q35" s="0" t="n">
+      <c r="Q35" s="1" t="n">
         <v>0.990670653996181</v>
       </c>
-      <c r="R35" s="0" t="n">
+      <c r="R35" s="1" t="n">
         <v>0.526988936981655</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="L36" s="0" t="n">
+      <c r="L36" s="1" t="n">
         <v>0.310705510900574</v>
       </c>
-      <c r="M36" s="0" t="n">
+      <c r="M36" s="1" t="n">
         <v>0.615480699777199</v>
       </c>
-      <c r="N36" s="0" t="n">
+      <c r="N36" s="1" t="n">
         <v>0.998483391091235</v>
       </c>
-      <c r="O36" s="0" t="n">
+      <c r="O36" s="1" t="n">
         <v>0.504278227012298</v>
       </c>
-      <c r="P36" s="0" t="n">
+      <c r="P36" s="1" t="n">
         <v>0.0875256134525823</v>
       </c>
-      <c r="Q36" s="0" t="n">
+      <c r="Q36" s="1" t="n">
         <v>0.462288452697001</v>
       </c>
-      <c r="R36" s="0" t="n">
+      <c r="R36" s="1" t="n">
         <v>0.562843420608801</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L37" s="0" t="n">
+      <c r="L37" s="1" t="n">
         <v>0.439263017872823</v>
       </c>
-      <c r="M37" s="0" t="n">
+      <c r="M37" s="1" t="n">
         <v>0.0752928224532246</v>
       </c>
-      <c r="N37" s="0" t="n">
+      <c r="N37" s="1" t="n">
         <v>0.0973139694314581</v>
       </c>
-      <c r="O37" s="0" t="n">
+      <c r="O37" s="1" t="n">
         <v>0.118535142325885</v>
       </c>
-      <c r="P37" s="0" t="n">
+      <c r="P37" s="1" t="n">
         <v>0.764658026770692</v>
       </c>
-      <c r="Q37" s="0" t="n">
+      <c r="Q37" s="1" t="n">
         <v>0.893320427640006</v>
       </c>
-      <c r="R37" s="0" t="n">
+      <c r="R37" s="1" t="n">
         <v>0.369172021408058</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L38" s="0" t="n">
+      <c r="L38" s="1" t="n">
         <v>0.0273297160175079</v>
       </c>
-      <c r="M38" s="0" t="n">
+      <c r="M38" s="1" t="n">
         <v>0.610100540542761</v>
       </c>
-      <c r="N38" s="0" t="n">
+      <c r="N38" s="1" t="n">
         <v>0.523034825890827</v>
       </c>
-      <c r="O38" s="0" t="n">
+      <c r="O38" s="1" t="n">
         <v>0.294273476370596</v>
       </c>
-      <c r="P38" s="0" t="n">
+      <c r="P38" s="1" t="n">
         <v>0.876027812830023</v>
       </c>
-      <c r="Q38" s="0" t="n">
+      <c r="Q38" s="1" t="n">
         <v>0.946591816147745</v>
       </c>
-      <c r="R38" s="0" t="n">
+      <c r="R38" s="1" t="n">
         <v>0.328636361620051</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="L39" s="0" t="n">
+      <c r="L39" s="1" t="n">
         <v>0.0501955902408249</v>
       </c>
-      <c r="M39" s="0" t="n">
+      <c r="M39" s="1" t="n">
         <v>0.763686911335516</v>
       </c>
-      <c r="N39" s="0" t="n">
+      <c r="N39" s="1" t="n">
         <v>0.936693132835738</v>
       </c>
-      <c r="O39" s="0" t="n">
+      <c r="O39" s="1" t="n">
         <v>0.526876131680729</v>
       </c>
-      <c r="P39" s="0" t="n">
+      <c r="P39" s="1" t="n">
         <v>0.384057553645162</v>
       </c>
-      <c r="Q39" s="0" t="n">
+      <c r="Q39" s="1" t="n">
         <v>0.964063429617191</v>
       </c>
-      <c r="R39" s="0" t="n">
+      <c r="R39" s="1" t="n">
         <v>0.582490046567509</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L40" s="0" t="n">
+      <c r="L40" s="1" t="n">
         <v>0.273687996920313</v>
       </c>
-      <c r="M40" s="0" t="n">
+      <c r="M40" s="1" t="n">
         <v>0.636128995056395</v>
       </c>
-      <c r="N40" s="0" t="n">
+      <c r="N40" s="1" t="n">
         <v>0.581423185150859</v>
       </c>
-      <c r="O40" s="0" t="n">
+      <c r="O40" s="1" t="n">
         <v>0.176445657899838</v>
       </c>
-      <c r="P40" s="0" t="n">
+      <c r="P40" s="1" t="n">
         <v>0.115225631238025</v>
       </c>
-      <c r="Q40" s="0" t="n">
+      <c r="Q40" s="1" t="n">
         <v>0.789625265007145</v>
       </c>
-      <c r="R40" s="0" t="n">
+      <c r="R40" s="1" t="n">
         <v>0.784078933869584</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="L41" s="0" t="n">
+      <c r="L41" s="1" t="n">
         <v>0.553405555572344</v>
       </c>
-      <c r="M41" s="0" t="n">
+      <c r="M41" s="1" t="n">
         <v>0.575857431069105</v>
       </c>
-      <c r="N41" s="0" t="n">
+      <c r="N41" s="1" t="n">
         <v>0.0502672966691989</v>
       </c>
-      <c r="O41" s="0" t="n">
+      <c r="O41" s="1" t="n">
         <v>0.00527914090736481</v>
       </c>
-      <c r="P41" s="0" t="n">
+      <c r="P41" s="1" t="n">
         <v>0.659433591844401</v>
       </c>
-      <c r="Q41" s="0" t="n">
+      <c r="Q41" s="1" t="n">
         <v>0.997941212376707</v>
       </c>
-      <c r="R41" s="0" t="n">
+      <c r="R41" s="1" t="n">
         <v>0.939731256208892</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="L42" s="0" t="n">
+      <c r="L42" s="1" t="n">
         <v>0.710532187831164</v>
       </c>
-      <c r="M42" s="0" t="n">
+      <c r="M42" s="1" t="n">
         <v>0.343891426227658</v>
       </c>
-      <c r="N42" s="0" t="n">
+      <c r="N42" s="1" t="n">
         <v>0.384823655481262</v>
       </c>
-      <c r="O42" s="0" t="n">
+      <c r="O42" s="1" t="n">
         <v>0.912840513675887</v>
       </c>
-      <c r="P42" s="0" t="n">
+      <c r="P42" s="1" t="n">
         <v>0.228031016663291</v>
       </c>
-      <c r="Q42" s="0" t="n">
+      <c r="Q42" s="1" t="n">
         <v>0.335344095903155</v>
       </c>
-      <c r="R42" s="0" t="n">
+      <c r="R42" s="1" t="n">
         <v>0.0326724603335776</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L43" s="0" t="n">
+      <c r="L43" s="1" t="n">
         <v>0.600354862054731</v>
       </c>
-      <c r="M43" s="0" t="n">
+      <c r="M43" s="1" t="n">
         <v>0.653806671834964</v>
       </c>
-      <c r="N43" s="0" t="n">
+      <c r="N43" s="1" t="n">
         <v>0.471066955141406</v>
       </c>
-      <c r="O43" s="0" t="n">
+      <c r="O43" s="1" t="n">
         <v>0.0923174931552383</v>
       </c>
-      <c r="P43" s="0" t="n">
+      <c r="P43" s="1" t="n">
         <v>0.22759091120234</v>
       </c>
-      <c r="Q43" s="0" t="n">
+      <c r="Q43" s="1" t="n">
         <v>0.173216848921335</v>
       </c>
-      <c r="R43" s="0" t="n">
+      <c r="R43" s="1" t="n">
         <v>0.573774228177089</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L44" s="0" t="n">
+      <c r="L44" s="1" t="n">
         <v>0.917780517589332</v>
       </c>
-      <c r="M44" s="0" t="n">
+      <c r="M44" s="1" t="n">
         <v>0.149385919903291</v>
       </c>
-      <c r="N44" s="0" t="n">
+      <c r="N44" s="1" t="n">
         <v>0.03075667467921</v>
       </c>
-      <c r="O44" s="0" t="n">
+      <c r="O44" s="1" t="n">
         <v>0.800445368562611</v>
       </c>
-      <c r="P44" s="0" t="n">
+      <c r="P44" s="1" t="n">
         <v>0.935646921887447</v>
       </c>
-      <c r="Q44" s="0" t="n">
+      <c r="Q44" s="1" t="n">
         <v>0.700635133264883</v>
       </c>
-      <c r="R44" s="0" t="n">
+      <c r="R44" s="1" t="n">
         <v>0.780531009221096</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="L45" s="0" t="n">
+      <c r="L45" s="1" t="n">
         <v>0.986746239438198</v>
       </c>
-      <c r="M45" s="0" t="n">
+      <c r="M45" s="1" t="n">
         <v>0.527954419892915</v>
       </c>
-      <c r="N45" s="0" t="n">
+      <c r="N45" s="1" t="n">
         <v>0.767270355017595</v>
       </c>
-      <c r="O45" s="0" t="n">
+      <c r="O45" s="1" t="n">
         <v>0.794885212837792</v>
       </c>
-      <c r="P45" s="0" t="n">
+      <c r="P45" s="1" t="n">
         <v>0.198119293970352</v>
       </c>
-      <c r="Q45" s="0" t="n">
+      <c r="Q45" s="1" t="n">
         <v>0.177635635566979</v>
       </c>
-      <c r="R45" s="0" t="n">
+      <c r="R45" s="1" t="n">
         <v>0.874830006937173</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L46" s="0" t="n">
+      <c r="L46" s="1" t="n">
         <v>0.993736391918462</v>
       </c>
-      <c r="M46" s="0" t="n">
+      <c r="M46" s="1" t="n">
         <v>0.2755163089957</v>
       </c>
-      <c r="N46" s="0" t="n">
+      <c r="N46" s="1" t="n">
         <v>0.26303429307535</v>
       </c>
-      <c r="O46" s="0" t="n">
+      <c r="O46" s="1" t="n">
         <v>0.380903985808777</v>
       </c>
-      <c r="P46" s="0" t="n">
+      <c r="P46" s="1" t="n">
         <v>0.823586588546092</v>
       </c>
-      <c r="Q46" s="0" t="n">
+      <c r="Q46" s="1" t="n">
         <v>0.440639217417163</v>
       </c>
-      <c r="R46" s="0" t="n">
+      <c r="R46" s="1" t="n">
         <v>0.802030744043315</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L47" s="0" t="n">
+      <c r="L47" s="1" t="n">
         <v>0.866009327847726</v>
       </c>
-      <c r="M47" s="0" t="n">
+      <c r="M47" s="1" t="n">
         <v>0.992256787142238</v>
       </c>
-      <c r="N47" s="0" t="n">
+      <c r="N47" s="1" t="n">
         <v>0.701299389727113</v>
       </c>
-      <c r="O47" s="0" t="n">
+      <c r="O47" s="1" t="n">
         <v>0.254536599354126</v>
       </c>
-      <c r="P47" s="0" t="n">
+      <c r="P47" s="1" t="n">
         <v>0.543188541033287</v>
       </c>
-      <c r="Q47" s="0" t="n">
+      <c r="Q47" s="1" t="n">
         <v>0.580545728688512</v>
       </c>
-      <c r="R47" s="0" t="n">
+      <c r="R47" s="1" t="n">
         <v>0.461875572299574</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L48" s="0" t="n">
+      <c r="L48" s="1" t="n">
         <v>0.587973316119502</v>
       </c>
-      <c r="M48" s="0" t="n">
+      <c r="M48" s="1" t="n">
         <v>0.142677548392102</v>
       </c>
-      <c r="N48" s="0" t="n">
+      <c r="N48" s="1" t="n">
         <v>0.547495279818406</v>
       </c>
-      <c r="O48" s="0" t="n">
+      <c r="O48" s="1" t="n">
         <v>0.559284528790441</v>
       </c>
-      <c r="P48" s="0" t="n">
+      <c r="P48" s="1" t="n">
         <v>0.815984957261471</v>
       </c>
-      <c r="Q48" s="0" t="n">
+      <c r="Q48" s="1" t="n">
         <v>0.777386532590305</v>
       </c>
-      <c r="R48" s="0" t="n">
+      <c r="R48" s="1" t="n">
         <v>0.195453672193053</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="L49" s="0" t="n">
+      <c r="L49" s="1" t="n">
         <v>0.580041001463718</v>
       </c>
-      <c r="M49" s="0" t="n">
+      <c r="M49" s="1" t="n">
         <v>0.840555762180691</v>
       </c>
-      <c r="N49" s="0" t="n">
+      <c r="N49" s="1" t="n">
         <v>0.519022674327308</v>
       </c>
-      <c r="O49" s="0" t="n">
+      <c r="O49" s="1" t="n">
         <v>0.996820803338684</v>
       </c>
-      <c r="P49" s="0" t="n">
+      <c r="P49" s="1" t="n">
         <v>0.871816818467502</v>
       </c>
-      <c r="Q49" s="0" t="n">
+      <c r="Q49" s="1" t="n">
         <v>0.0556912241186601</v>
       </c>
-      <c r="R49" s="0" t="n">
+      <c r="R49" s="1" t="n">
         <v>0.156072075951507</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L50" s="0" t="n">
+      <c r="L50" s="1" t="n">
         <v>0.018459623561665</v>
       </c>
-      <c r="M50" s="0" t="n">
+      <c r="M50" s="1" t="n">
         <v>0.362233557798657</v>
       </c>
-      <c r="N50" s="0" t="n">
+      <c r="N50" s="1" t="n">
         <v>0.61664377986902</v>
       </c>
-      <c r="O50" s="0" t="n">
+      <c r="O50" s="1" t="n">
         <v>0.975196891147658</v>
       </c>
-      <c r="P50" s="0" t="n">
+      <c r="P50" s="1" t="n">
         <v>0.609911088106905</v>
       </c>
-      <c r="Q50" s="0" t="n">
+      <c r="Q50" s="1" t="n">
         <v>0.730229535253705</v>
       </c>
-      <c r="R50" s="0" t="n">
+      <c r="R50" s="1" t="n">
         <v>0.585163791328086</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L51" s="0" t="n">
+      <c r="L51" s="1" t="n">
         <v>0.214511253668006</v>
       </c>
-      <c r="M51" s="0" t="n">
+      <c r="M51" s="1" t="n">
         <v>0.441236679934384</v>
       </c>
-      <c r="N51" s="0" t="n">
+      <c r="N51" s="1" t="n">
         <v>0.07979228736901</v>
       </c>
-      <c r="O51" s="0" t="n">
+      <c r="O51" s="1" t="n">
         <v>0.0738801844592459</v>
       </c>
-      <c r="P51" s="0" t="n">
+      <c r="P51" s="1" t="n">
         <v>0.46451516966665</v>
       </c>
-      <c r="Q51" s="0" t="n">
+      <c r="Q51" s="1" t="n">
         <v>0.905115674349067</v>
       </c>
-      <c r="R51" s="0" t="n">
+      <c r="R51" s="1" t="n">
         <v>0.47172589283529</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L52" s="0" t="n">
+      <c r="L52" s="1" t="n">
         <v>0.299133276706589</v>
       </c>
-      <c r="M52" s="0" t="n">
+      <c r="M52" s="1" t="n">
         <v>0.972255814663594</v>
       </c>
-      <c r="N52" s="0" t="n">
+      <c r="N52" s="1" t="n">
         <v>0.090672897309258</v>
       </c>
-      <c r="O52" s="0" t="n">
+      <c r="O52" s="1" t="n">
         <v>0.826483715426013</v>
       </c>
-      <c r="P52" s="0" t="n">
+      <c r="P52" s="1" t="n">
         <v>0.548502748430025</v>
       </c>
-      <c r="Q52" s="0" t="n">
+      <c r="Q52" s="1" t="n">
         <v>0.0732742042370105</v>
       </c>
-      <c r="R52" s="0" t="n">
+      <c r="R52" s="1" t="n">
         <v>0.29841948246202</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L53" s="0" t="n">
+      <c r="L53" s="1" t="n">
         <v>0.044715484600623</v>
       </c>
-      <c r="M53" s="0" t="n">
+      <c r="M53" s="1" t="n">
         <v>0.556747538399581</v>
       </c>
-      <c r="N53" s="0" t="n">
+      <c r="N53" s="1" t="n">
         <v>0.365910887200341</v>
       </c>
-      <c r="O53" s="0" t="n">
+      <c r="O53" s="1" t="n">
         <v>0.542644007538047</v>
       </c>
-      <c r="P53" s="0" t="n">
+      <c r="P53" s="1" t="n">
         <v>0.517381242956151</v>
       </c>
-      <c r="Q53" s="0" t="n">
+      <c r="Q53" s="1" t="n">
         <v>0.44497916157816</v>
       </c>
-      <c r="R53" s="0" t="n">
+      <c r="R53" s="1" t="n">
         <v>0.540796213251348</v>
       </c>
     </row>
@@ -1927,1545 +1931,1545 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="B3" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A3,Sheet1!$B$3:$B$53,0),MATCH(B3,Sheet1!$L$1:$R$1,0))</f>
         <v>0.977263720980125</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="B4" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D4" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A4,Sheet1!$B$3:$B$53,0),MATCH(B4,Sheet1!$L$1:$R$1,0))</f>
         <v>0.942556599505759</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="B5" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A5,Sheet1!$B$3:$B$53,0),MATCH(B5,Sheet1!$L$1:$R$1,0))</f>
         <v>0.12448902388882</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="0" t="n">
+      <c r="B6" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A6,Sheet1!$B$3:$B$53,0),MATCH(B6,Sheet1!$L$1:$R$1,0))</f>
         <v>0.718263105033681</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="B7" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A7,Sheet1!$B$3:$B$53,0),MATCH(B7,Sheet1!$L$1:$R$1,0))</f>
         <v>0.676907924564291</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="0" t="n">
+      <c r="B8" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A8,Sheet1!$B$3:$B$53,0),MATCH(B8,Sheet1!$L$1:$R$1,0))</f>
         <v>0.287396920270059</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="B9" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D9" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A9,Sheet1!$B$3:$B$53,0),MATCH(B9,Sheet1!$L$1:$R$1,0))</f>
         <v>0.0920880379017474</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" s="0" t="n">
+      <c r="B10" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A10,Sheet1!$B$3:$B$53,0),MATCH(B10,Sheet1!$L$1:$R$1,0))</f>
         <v>0.43894251611377</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="B11" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A11,Sheet1!$B$3:$B$53,0),MATCH(B11,Sheet1!$L$1:$R$1,0))</f>
         <v>0.346262636077046</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D12" s="0" t="n">
+      <c r="B12" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A12,Sheet1!$B$3:$B$53,0),MATCH(B12,Sheet1!$L$1:$R$1,0))</f>
         <v>0.606937263920749</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="0" t="n">
+      <c r="B13" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A13,Sheet1!$B$3:$B$53,0),MATCH(B13,Sheet1!$L$1:$R$1,0))</f>
         <v>0.208578383160297</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="0" t="n">
+      <c r="B14" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D14" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A14,Sheet1!$B$3:$B$53,0),MATCH(B14,Sheet1!$L$1:$R$1,0))</f>
         <v>0.832246441364454</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D15" s="0" t="n">
+      <c r="B15" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D15" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A15,Sheet1!$B$3:$B$53,0),MATCH(B15,Sheet1!$L$1:$R$1,0))</f>
         <v>0.815765208709144</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="0" t="n">
+      <c r="B16" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A16,Sheet1!$B$3:$B$53,0),MATCH(B16,Sheet1!$L$1:$R$1,0))</f>
         <v>0.984343202798317</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="0" t="n">
+      <c r="B17" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D17" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A17,Sheet1!$B$3:$B$53,0),MATCH(B17,Sheet1!$L$1:$R$1,0))</f>
         <v>0.589511751085022</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D18" s="0" t="n">
+      <c r="B18" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A18,Sheet1!$B$3:$B$53,0),MATCH(B18,Sheet1!$L$1:$R$1,0))</f>
         <v>0.934109273163392</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="0" t="n">
+      <c r="B19" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A19,Sheet1!$B$3:$B$53,0),MATCH(B19,Sheet1!$L$1:$R$1,0))</f>
         <v>0.111624290674215</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D20" s="0" t="n">
+      <c r="B20" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D20" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A20,Sheet1!$B$3:$B$53,0),MATCH(B20,Sheet1!$L$1:$R$1,0))</f>
         <v>0.310555350830881</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="0" t="n">
+      <c r="B21" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A21,Sheet1!$B$3:$B$53,0),MATCH(B21,Sheet1!$L$1:$R$1,0))</f>
         <v>0.081325519667791</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D22" s="0" t="n">
+      <c r="B22" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A22,Sheet1!$B$3:$B$53,0),MATCH(B22,Sheet1!$L$1:$R$1,0))</f>
         <v>0.460078181606601</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D23" s="0" t="n">
+      <c r="B23" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A23,Sheet1!$B$3:$B$53,0),MATCH(B23,Sheet1!$L$1:$R$1,0))</f>
         <v>0.922944198286225</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" s="0" t="n">
+      <c r="B24" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A24,Sheet1!$B$3:$B$53,0),MATCH(B24,Sheet1!$L$1:$R$1,0))</f>
         <v>0.293275438338128</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="0" t="n">
+      <c r="B25" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A25,Sheet1!$B$3:$B$53,0),MATCH(B25,Sheet1!$L$1:$R$1,0))</f>
         <v>0.151646652406461</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="0" t="n">
+      <c r="B26" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A26,Sheet1!$B$3:$B$53,0),MATCH(B26,Sheet1!$L$1:$R$1,0))</f>
         <v>0.483752214444178</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D27" s="0" t="n">
+      <c r="B27" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A27,Sheet1!$B$3:$B$53,0),MATCH(B27,Sheet1!$L$1:$R$1,0))</f>
         <v>0.202779968226557</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="0" t="n">
+      <c r="B28" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A28,Sheet1!$B$3:$B$53,0),MATCH(B28,Sheet1!$L$1:$R$1,0))</f>
         <v>0.550544014823825</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="0" t="n">
+      <c r="B29" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A29,Sheet1!$B$3:$B$53,0),MATCH(B29,Sheet1!$L$1:$R$1,0))</f>
         <v>0.890567115157197</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" s="0" t="n">
+      <c r="B30" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D30" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A30,Sheet1!$B$3:$B$53,0),MATCH(B30,Sheet1!$L$1:$R$1,0))</f>
         <v>0.202300147891679</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D31" s="0" t="n">
+      <c r="B31" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D31" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A31,Sheet1!$B$3:$B$53,0),MATCH(B31,Sheet1!$L$1:$R$1,0))</f>
         <v>0.00735575830023227</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="0" t="n">
+      <c r="B32" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A32,Sheet1!$B$3:$B$53,0),MATCH(B32,Sheet1!$L$1:$R$1,0))</f>
         <v>0.496075380477184</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="0" t="n">
+      <c r="B33" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D33" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A33,Sheet1!$B$3:$B$53,0),MATCH(B33,Sheet1!$L$1:$R$1,0))</f>
         <v>0.558832213932223</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D34" s="0" t="n">
+      <c r="B34" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D34" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A34,Sheet1!$B$3:$B$53,0),MATCH(B34,Sheet1!$L$1:$R$1,0))</f>
         <v>0.0428436978656417</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D35" s="0" t="n">
+      <c r="B35" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D35" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A35,Sheet1!$B$3:$B$53,0),MATCH(B35,Sheet1!$L$1:$R$1,0))</f>
         <v>0.882410020278209</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D36" s="0" t="n">
+      <c r="B36" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D36" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A36,Sheet1!$B$3:$B$53,0),MATCH(B36,Sheet1!$L$1:$R$1,0))</f>
         <v>0.310705510900574</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D37" s="0" t="n">
+      <c r="B37" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D37" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A37,Sheet1!$B$3:$B$53,0),MATCH(B37,Sheet1!$L$1:$R$1,0))</f>
         <v>0.439263017872823</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D38" s="0" t="n">
+      <c r="B38" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D38" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A38,Sheet1!$B$3:$B$53,0),MATCH(B38,Sheet1!$L$1:$R$1,0))</f>
         <v>0.0273297160175079</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D39" s="0" t="n">
+      <c r="B39" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D39" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A39,Sheet1!$B$3:$B$53,0),MATCH(B39,Sheet1!$L$1:$R$1,0))</f>
         <v>0.0501955902408249</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40" s="0" t="n">
+      <c r="B40" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A40,Sheet1!$B$3:$B$53,0),MATCH(B40,Sheet1!$L$1:$R$1,0))</f>
         <v>0.273687996920313</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D41" s="0" t="n">
+      <c r="B41" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D41" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A41,Sheet1!$B$3:$B$53,0),MATCH(B41,Sheet1!$L$1:$R$1,0))</f>
         <v>0.553405555572344</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D42" s="0" t="n">
+      <c r="B42" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A42,Sheet1!$B$3:$B$53,0),MATCH(B42,Sheet1!$L$1:$R$1,0))</f>
         <v>0.710532187831164</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D43" s="0" t="n">
+      <c r="B43" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A43,Sheet1!$B$3:$B$53,0),MATCH(B43,Sheet1!$L$1:$R$1,0))</f>
         <v>0.600354862054731</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B44" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D44" s="0" t="n">
+      <c r="B44" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D44" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A44,Sheet1!$B$3:$B$53,0),MATCH(B44,Sheet1!$L$1:$R$1,0))</f>
         <v>0.917780517589332</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B45" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D45" s="0" t="n">
+      <c r="B45" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A45,Sheet1!$B$3:$B$53,0),MATCH(B45,Sheet1!$L$1:$R$1,0))</f>
         <v>0.986746239438198</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B46" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D46" s="0" t="n">
+      <c r="B46" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D46" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A46,Sheet1!$B$3:$B$53,0),MATCH(B46,Sheet1!$L$1:$R$1,0))</f>
         <v>0.993736391918462</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B47" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D47" s="0" t="n">
+      <c r="B47" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D47" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A47,Sheet1!$B$3:$B$53,0),MATCH(B47,Sheet1!$L$1:$R$1,0))</f>
         <v>0.866009327847726</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B48" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D48" s="0" t="n">
+      <c r="B48" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A48,Sheet1!$B$3:$B$53,0),MATCH(B48,Sheet1!$L$1:$R$1,0))</f>
         <v>0.587973316119502</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B49" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D49" s="0" t="n">
+      <c r="B49" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A49,Sheet1!$B$3:$B$53,0),MATCH(B49,Sheet1!$L$1:$R$1,0))</f>
         <v>0.580041001463718</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B50" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D50" s="0" t="n">
+      <c r="B50" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D50" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A50,Sheet1!$B$3:$B$53,0),MATCH(B50,Sheet1!$L$1:$R$1,0))</f>
         <v>0.018459623561665</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B51" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D51" s="0" t="n">
+      <c r="B51" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A51,Sheet1!$B$3:$B$53,0),MATCH(B51,Sheet1!$L$1:$R$1,0))</f>
         <v>0.214511253668006</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D52" s="0" t="n">
+      <c r="B52" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A52,Sheet1!$B$3:$B$53,0),MATCH(B52,Sheet1!$L$1:$R$1,0))</f>
         <v>0.299133276706589</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B53" s="1" t="n">
-        <v>2015</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D53" s="0" t="n">
+      <c r="B53" s="2" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D53" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A53,Sheet1!$B$3:$B$53,0),MATCH(B53,Sheet1!$L$1:$R$1,0))</f>
         <v>0.044715484600623</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B54" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D54" s="0" t="n">
+      <c r="B54" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D54" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A54,Sheet1!$B$3:$B$53,0),MATCH(B54,Sheet1!$L$1:$R$1,0))</f>
         <v>0.369694550249851</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="2" t="s">
+      <c r="A55" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B55" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D55" s="0" t="n">
+      <c r="B55" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D55" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A55,Sheet1!$B$3:$B$53,0),MATCH(B55,Sheet1!$L$1:$R$1,0))</f>
         <v>0.718165777391587</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
+      <c r="A56" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B56" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D56" s="0" t="n">
+      <c r="B56" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D56" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A56,Sheet1!$B$3:$B$53,0),MATCH(B56,Sheet1!$L$1:$R$1,0))</f>
         <v>0.647574861591199</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B57" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D57" s="0" t="n">
+      <c r="B57" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D57" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A57,Sheet1!$B$3:$B$53,0),MATCH(B57,Sheet1!$L$1:$R$1,0))</f>
         <v>0.918250677089609</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B58" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D58" s="0" t="n">
+      <c r="B58" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D58" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A58,Sheet1!$B$3:$B$53,0),MATCH(B58,Sheet1!$L$1:$R$1,0))</f>
         <v>0.470295046817084</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B59" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D59" s="0" t="n">
+      <c r="B59" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D59" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A59,Sheet1!$B$3:$B$53,0),MATCH(B59,Sheet1!$L$1:$R$1,0))</f>
         <v>0.56978655216477</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B60" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D60" s="0" t="n">
+      <c r="B60" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A60,Sheet1!$B$3:$B$53,0),MATCH(B60,Sheet1!$L$1:$R$1,0))</f>
         <v>0.314761212646374</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B61" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D61" s="0" t="n">
+      <c r="B61" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D61" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A61,Sheet1!$B$3:$B$53,0),MATCH(B61,Sheet1!$L$1:$R$1,0))</f>
         <v>0.619263449452447</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B62" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D62" s="0" t="n">
+      <c r="B62" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D62" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A62,Sheet1!$B$3:$B$53,0),MATCH(B62,Sheet1!$L$1:$R$1,0))</f>
         <v>0.422234596278344</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B63" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D63" s="0" t="n">
+      <c r="B63" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D63" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A63,Sheet1!$B$3:$B$53,0),MATCH(B63,Sheet1!$L$1:$R$1,0))</f>
         <v>0.110630909969275</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B64" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D64" s="0" t="n">
+      <c r="B64" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D64" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A64,Sheet1!$B$3:$B$53,0),MATCH(B64,Sheet1!$L$1:$R$1,0))</f>
         <v>0.504589039555236</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B65" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D65" s="0" t="n">
+      <c r="B65" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D65" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A65,Sheet1!$B$3:$B$53,0),MATCH(B65,Sheet1!$L$1:$R$1,0))</f>
         <v>0.561936675559634</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B66" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D66" s="0" t="n">
+      <c r="B66" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D66" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A66,Sheet1!$B$3:$B$53,0),MATCH(B66,Sheet1!$L$1:$R$1,0))</f>
         <v>0.0121997857164132</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B67" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D67" s="0" t="n">
+      <c r="B67" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D67" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A67,Sheet1!$B$3:$B$53,0),MATCH(B67,Sheet1!$L$1:$R$1,0))</f>
         <v>0.0744918816064607</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B68" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D68" s="0" t="n">
+      <c r="B68" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D68" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A68,Sheet1!$B$3:$B$53,0),MATCH(B68,Sheet1!$L$1:$R$1,0))</f>
         <v>0.101270170745148</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+      <c r="A69" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B69" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D69" s="0" t="n">
+      <c r="B69" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D69" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A69,Sheet1!$B$3:$B$53,0),MATCH(B69,Sheet1!$L$1:$R$1,0))</f>
         <v>0.444939584993711</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="s">
+      <c r="A70" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B70" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D70" s="0" t="n">
+      <c r="B70" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D70" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A70,Sheet1!$B$3:$B$53,0),MATCH(B70,Sheet1!$L$1:$R$1,0))</f>
         <v>0.813128951408209</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="2" t="s">
+      <c r="A71" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B71" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D71" s="0" t="n">
+      <c r="B71" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D71" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A71,Sheet1!$B$3:$B$53,0),MATCH(B71,Sheet1!$L$1:$R$1,0))</f>
         <v>0.833368049338167</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
+      <c r="A72" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B72" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D72" s="0" t="n">
+      <c r="B72" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D72" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A72,Sheet1!$B$3:$B$53,0),MATCH(B72,Sheet1!$L$1:$R$1,0))</f>
         <v>0.980309702492869</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="2" t="s">
+      <c r="A73" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B73" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D73" s="0" t="n">
+      <c r="B73" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D73" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A73,Sheet1!$B$3:$B$53,0),MATCH(B73,Sheet1!$L$1:$R$1,0))</f>
         <v>0.167787479706479</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="s">
+      <c r="A74" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B74" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D74" s="0" t="n">
+      <c r="B74" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D74" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A74,Sheet1!$B$3:$B$53,0),MATCH(B74,Sheet1!$L$1:$R$1,0))</f>
         <v>0.745094760504618</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
+      <c r="A75" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B75" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D75" s="0" t="n">
+      <c r="B75" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D75" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A75,Sheet1!$B$3:$B$53,0),MATCH(B75,Sheet1!$L$1:$R$1,0))</f>
         <v>0.392068209481472</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
+      <c r="A76" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B76" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D76" s="0" t="n">
+      <c r="B76" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D76" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A76,Sheet1!$B$3:$B$53,0),MATCH(B76,Sheet1!$L$1:$R$1,0))</f>
         <v>0.404066649594268</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="s">
+      <c r="A77" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B77" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D77" s="0" t="n">
+      <c r="B77" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D77" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A77,Sheet1!$B$3:$B$53,0),MATCH(B77,Sheet1!$L$1:$R$1,0))</f>
         <v>0.962098177585588</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
+      <c r="A78" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B78" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D78" s="0" t="n">
+      <c r="B78" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D78" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A78,Sheet1!$B$3:$B$53,0),MATCH(B78,Sheet1!$L$1:$R$1,0))</f>
         <v>0.0463131954792417</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2" t="s">
+      <c r="A79" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B79" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D79" s="0" t="n">
+      <c r="B79" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D79" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A79,Sheet1!$B$3:$B$53,0),MATCH(B79,Sheet1!$L$1:$R$1,0))</f>
         <v>0.987397660151677</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="s">
+      <c r="A80" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B80" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D80" s="0" t="n">
+      <c r="B80" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D80" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A80,Sheet1!$B$3:$B$53,0),MATCH(B80,Sheet1!$L$1:$R$1,0))</f>
         <v>0.434370975072386</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2" t="s">
+      <c r="A81" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B81" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D81" s="0" t="n">
+      <c r="B81" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D81" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A81,Sheet1!$B$3:$B$53,0),MATCH(B81,Sheet1!$L$1:$R$1,0))</f>
         <v>0.778758181214608</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2" t="s">
+      <c r="A82" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B82" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D82" s="0" t="n">
+      <c r="B82" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D82" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A82,Sheet1!$B$3:$B$53,0),MATCH(B82,Sheet1!$L$1:$R$1,0))</f>
         <v>0.997040199373517</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="s">
+      <c r="A83" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B83" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D83" s="0" t="n">
+      <c r="B83" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D83" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A83,Sheet1!$B$3:$B$53,0),MATCH(B83,Sheet1!$L$1:$R$1,0))</f>
         <v>0.546003573654997</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="s">
+      <c r="A84" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B84" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D84" s="0" t="n">
+      <c r="B84" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D84" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A84,Sheet1!$B$3:$B$53,0),MATCH(B84,Sheet1!$L$1:$R$1,0))</f>
         <v>0.0958252934572622</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="s">
+      <c r="A85" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B85" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D85" s="0" t="n">
+      <c r="B85" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D85" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A85,Sheet1!$B$3:$B$53,0),MATCH(B85,Sheet1!$L$1:$R$1,0))</f>
         <v>0.165230235461094</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="2" t="s">
+      <c r="A86" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B86" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D86" s="0" t="n">
+      <c r="B86" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D86" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A86,Sheet1!$B$3:$B$53,0),MATCH(B86,Sheet1!$L$1:$R$1,0))</f>
         <v>0.607227175985319</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2" t="s">
+      <c r="A87" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B87" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D87" s="0" t="n">
+      <c r="B87" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D87" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A87,Sheet1!$B$3:$B$53,0),MATCH(B87,Sheet1!$L$1:$R$1,0))</f>
         <v>0.615480699777199</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2" t="s">
+      <c r="A88" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B88" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D88" s="0" t="n">
+      <c r="B88" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D88" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A88,Sheet1!$B$3:$B$53,0),MATCH(B88,Sheet1!$L$1:$R$1,0))</f>
         <v>0.0752928224532246</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="s">
+      <c r="A89" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B89" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D89" s="0" t="n">
+      <c r="B89" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D89" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A89,Sheet1!$B$3:$B$53,0),MATCH(B89,Sheet1!$L$1:$R$1,0))</f>
         <v>0.610100540542761</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B90" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D90" s="0" t="n">
+      <c r="B90" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D90" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A90,Sheet1!$B$3:$B$53,0),MATCH(B90,Sheet1!$L$1:$R$1,0))</f>
         <v>0.763686911335516</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2" t="s">
+      <c r="A91" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B91" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D91" s="0" t="n">
+      <c r="B91" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D91" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A91,Sheet1!$B$3:$B$53,0),MATCH(B91,Sheet1!$L$1:$R$1,0))</f>
         <v>0.636128995056395</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B92" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D92" s="0" t="n">
+      <c r="B92" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D92" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A92,Sheet1!$B$3:$B$53,0),MATCH(B92,Sheet1!$L$1:$R$1,0))</f>
         <v>0.575857431069105</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="2" t="s">
+      <c r="A93" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B93" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D93" s="0" t="n">
+      <c r="B93" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D93" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A93,Sheet1!$B$3:$B$53,0),MATCH(B93,Sheet1!$L$1:$R$1,0))</f>
         <v>0.343891426227658</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2" t="s">
+      <c r="A94" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B94" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D94" s="0" t="n">
+      <c r="B94" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D94" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A94,Sheet1!$B$3:$B$53,0),MATCH(B94,Sheet1!$L$1:$R$1,0))</f>
         <v>0.653806671834964</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="s">
+      <c r="A95" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B95" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D95" s="0" t="n">
+      <c r="B95" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D95" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A95,Sheet1!$B$3:$B$53,0),MATCH(B95,Sheet1!$L$1:$R$1,0))</f>
         <v>0.149385919903291</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="s">
+      <c r="A96" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B96" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D96" s="0" t="n">
+      <c r="B96" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D96" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A96,Sheet1!$B$3:$B$53,0),MATCH(B96,Sheet1!$L$1:$R$1,0))</f>
         <v>0.527954419892915</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="s">
+      <c r="A97" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B97" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D97" s="0" t="n">
+      <c r="B97" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D97" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A97,Sheet1!$B$3:$B$53,0),MATCH(B97,Sheet1!$L$1:$R$1,0))</f>
         <v>0.2755163089957</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="s">
+      <c r="A98" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B98" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D98" s="0" t="n">
+      <c r="B98" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D98" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A98,Sheet1!$B$3:$B$53,0),MATCH(B98,Sheet1!$L$1:$R$1,0))</f>
         <v>0.992256787142238</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="2" t="s">
+      <c r="A99" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B99" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D99" s="0" t="n">
+      <c r="B99" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D99" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A99,Sheet1!$B$3:$B$53,0),MATCH(B99,Sheet1!$L$1:$R$1,0))</f>
         <v>0.142677548392102</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2" t="s">
+      <c r="A100" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B100" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D100" s="0" t="n">
+      <c r="B100" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D100" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A100,Sheet1!$B$3:$B$53,0),MATCH(B100,Sheet1!$L$1:$R$1,0))</f>
         <v>0.840555762180691</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="2" t="s">
+      <c r="A101" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B101" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D101" s="0" t="n">
+      <c r="B101" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D101" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A101,Sheet1!$B$3:$B$53,0),MATCH(B101,Sheet1!$L$1:$R$1,0))</f>
         <v>0.362233557798657</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2" t="s">
+      <c r="A102" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B102" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D102" s="0" t="n">
+      <c r="B102" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D102" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A102,Sheet1!$B$3:$B$53,0),MATCH(B102,Sheet1!$L$1:$R$1,0))</f>
         <v>0.441236679934384</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2" t="s">
+      <c r="A103" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B103" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D103" s="0" t="n">
+      <c r="B103" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D103" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A103,Sheet1!$B$3:$B$53,0),MATCH(B103,Sheet1!$L$1:$R$1,0))</f>
         <v>0.972255814663594</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="s">
+      <c r="A104" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B104" s="2" t="n">
-        <v>2016</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D104" s="0" t="n">
+      <c r="B104" s="3" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D104" s="1" t="n">
         <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A104,Sheet1!$B$3:$B$53,0),MATCH(B104,Sheet1!$L$1:$R$1,0))</f>
         <v>0.556747538399581</v>
       </c>

--- a/outputs/44296.xlsx
+++ b/outputs/44296.xlsx
@@ -1955,8 +1955,8 @@
         <v>57</v>
       </c>
       <c r="D3" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A3,Sheet1!$B$3:$B$53,0),MATCH(B3,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.977263720980125</v>
+        <f aca="false">IF(AND($A3="",$B3=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A3,Sheet1!$B$3:$B$53,0),MATCH($B3,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1970,8 +1970,8 @@
         <v>57</v>
       </c>
       <c r="D4" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A4,Sheet1!$B$3:$B$53,0),MATCH(B4,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.942556599505759</v>
+        <f aca="false">IF(AND($A4="",$B4=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A4,Sheet1!$B$3:$B$53,0),MATCH($B4,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.977263720980125</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1985,8 +1985,8 @@
         <v>57</v>
       </c>
       <c r="D5" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A5,Sheet1!$B$3:$B$53,0),MATCH(B5,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.12448902388882</v>
+        <f aca="false">IF(AND($A5="",$B5=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A5,Sheet1!$B$3:$B$53,0),MATCH($B5,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.942556599505759</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2000,8 +2000,8 @@
         <v>57</v>
       </c>
       <c r="D6" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A6,Sheet1!$B$3:$B$53,0),MATCH(B6,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.718263105033681</v>
+        <f aca="false">IF(AND($A6="",$B6=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A6,Sheet1!$B$3:$B$53,0),MATCH($B6,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.12448902388882</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2015,8 +2015,8 @@
         <v>57</v>
       </c>
       <c r="D7" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A7,Sheet1!$B$3:$B$53,0),MATCH(B7,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.676907924564291</v>
+        <f aca="false">IF(AND($A7="",$B7=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A7,Sheet1!$B$3:$B$53,0),MATCH($B7,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.718263105033681</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2030,8 +2030,8 @@
         <v>57</v>
       </c>
       <c r="D8" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A8,Sheet1!$B$3:$B$53,0),MATCH(B8,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.287396920270059</v>
+        <f aca="false">IF(AND($A8="",$B8=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A8,Sheet1!$B$3:$B$53,0),MATCH($B8,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.676907924564291</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2045,8 +2045,8 @@
         <v>57</v>
       </c>
       <c r="D9" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A9,Sheet1!$B$3:$B$53,0),MATCH(B9,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.0920880379017474</v>
+        <f aca="false">IF(AND($A9="",$B9=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A9,Sheet1!$B$3:$B$53,0),MATCH($B9,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.287396920270059</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2060,8 +2060,8 @@
         <v>57</v>
       </c>
       <c r="D10" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A10,Sheet1!$B$3:$B$53,0),MATCH(B10,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.43894251611377</v>
+        <f aca="false">IF(AND($A10="",$B10=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A10,Sheet1!$B$3:$B$53,0),MATCH($B10,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.0920880379017474</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2075,8 +2075,8 @@
         <v>57</v>
       </c>
       <c r="D11" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A11,Sheet1!$B$3:$B$53,0),MATCH(B11,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.346262636077046</v>
+        <f aca="false">IF(AND($A11="",$B11=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A11,Sheet1!$B$3:$B$53,0),MATCH($B11,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.43894251611377</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2090,8 +2090,8 @@
         <v>57</v>
       </c>
       <c r="D12" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A12,Sheet1!$B$3:$B$53,0),MATCH(B12,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.606937263920749</v>
+        <f aca="false">IF(AND($A12="",$B12=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A12,Sheet1!$B$3:$B$53,0),MATCH($B12,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.346262636077046</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2105,8 +2105,8 @@
         <v>57</v>
       </c>
       <c r="D13" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A13,Sheet1!$B$3:$B$53,0),MATCH(B13,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.208578383160297</v>
+        <f aca="false">IF(AND($A13="",$B13=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A13,Sheet1!$B$3:$B$53,0),MATCH($B13,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.606937263920749</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2120,8 +2120,8 @@
         <v>57</v>
       </c>
       <c r="D14" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A14,Sheet1!$B$3:$B$53,0),MATCH(B14,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.832246441364454</v>
+        <f aca="false">IF(AND($A14="",$B14=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A14,Sheet1!$B$3:$B$53,0),MATCH($B14,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.208578383160297</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2135,8 +2135,8 @@
         <v>57</v>
       </c>
       <c r="D15" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A15,Sheet1!$B$3:$B$53,0),MATCH(B15,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.815765208709144</v>
+        <f aca="false">IF(AND($A15="",$B15=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A15,Sheet1!$B$3:$B$53,0),MATCH($B15,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.832246441364454</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2150,8 +2150,8 @@
         <v>57</v>
       </c>
       <c r="D16" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A16,Sheet1!$B$3:$B$53,0),MATCH(B16,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.984343202798317</v>
+        <f aca="false">IF(AND($A16="",$B16=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A16,Sheet1!$B$3:$B$53,0),MATCH($B16,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.815765208709144</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2165,8 +2165,8 @@
         <v>57</v>
       </c>
       <c r="D17" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A17,Sheet1!$B$3:$B$53,0),MATCH(B17,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.589511751085022</v>
+        <f aca="false">IF(AND($A17="",$B17=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A17,Sheet1!$B$3:$B$53,0),MATCH($B17,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.984343202798317</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2180,8 +2180,8 @@
         <v>57</v>
       </c>
       <c r="D18" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A18,Sheet1!$B$3:$B$53,0),MATCH(B18,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.934109273163392</v>
+        <f aca="false">IF(AND($A18="",$B18=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A18,Sheet1!$B$3:$B$53,0),MATCH($B18,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.589511751085022</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2195,8 +2195,8 @@
         <v>57</v>
       </c>
       <c r="D19" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A19,Sheet1!$B$3:$B$53,0),MATCH(B19,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.111624290674215</v>
+        <f aca="false">IF(AND($A19="",$B19=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A19,Sheet1!$B$3:$B$53,0),MATCH($B19,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.934109273163392</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2210,8 +2210,8 @@
         <v>57</v>
       </c>
       <c r="D20" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A20,Sheet1!$B$3:$B$53,0),MATCH(B20,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.310555350830881</v>
+        <f aca="false">IF(AND($A20="",$B20=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A20,Sheet1!$B$3:$B$53,0),MATCH($B20,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.111624290674215</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2225,8 +2225,8 @@
         <v>57</v>
       </c>
       <c r="D21" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A21,Sheet1!$B$3:$B$53,0),MATCH(B21,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.081325519667791</v>
+        <f aca="false">IF(AND($A21="",$B21=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A21,Sheet1!$B$3:$B$53,0),MATCH($B21,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.310555350830881</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2240,8 +2240,8 @@
         <v>57</v>
       </c>
       <c r="D22" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A22,Sheet1!$B$3:$B$53,0),MATCH(B22,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.460078181606601</v>
+        <f aca="false">IF(AND($A22="",$B22=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A22,Sheet1!$B$3:$B$53,0),MATCH($B22,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.081325519667791</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2255,8 +2255,8 @@
         <v>57</v>
       </c>
       <c r="D23" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A23,Sheet1!$B$3:$B$53,0),MATCH(B23,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.922944198286225</v>
+        <f aca="false">IF(AND($A23="",$B23=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A23,Sheet1!$B$3:$B$53,0),MATCH($B23,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.460078181606601</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2270,8 +2270,8 @@
         <v>57</v>
       </c>
       <c r="D24" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A24,Sheet1!$B$3:$B$53,0),MATCH(B24,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.293275438338128</v>
+        <f aca="false">IF(AND($A24="",$B24=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A24,Sheet1!$B$3:$B$53,0),MATCH($B24,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.922944198286225</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2285,8 +2285,8 @@
         <v>57</v>
       </c>
       <c r="D25" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A25,Sheet1!$B$3:$B$53,0),MATCH(B25,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.151646652406461</v>
+        <f aca="false">IF(AND($A25="",$B25=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A25,Sheet1!$B$3:$B$53,0),MATCH($B25,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.293275438338128</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2300,8 +2300,8 @@
         <v>57</v>
       </c>
       <c r="D26" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A26,Sheet1!$B$3:$B$53,0),MATCH(B26,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.483752214444178</v>
+        <f aca="false">IF(AND($A26="",$B26=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A26,Sheet1!$B$3:$B$53,0),MATCH($B26,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.151646652406461</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2315,8 +2315,8 @@
         <v>57</v>
       </c>
       <c r="D27" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A27,Sheet1!$B$3:$B$53,0),MATCH(B27,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.202779968226557</v>
+        <f aca="false">IF(AND($A27="",$B27=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A27,Sheet1!$B$3:$B$53,0),MATCH($B27,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.483752214444178</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2330,8 +2330,8 @@
         <v>57</v>
       </c>
       <c r="D28" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A28,Sheet1!$B$3:$B$53,0),MATCH(B28,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.550544014823825</v>
+        <f aca="false">IF(AND($A28="",$B28=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A28,Sheet1!$B$3:$B$53,0),MATCH($B28,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.202779968226557</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2345,8 +2345,8 @@
         <v>57</v>
       </c>
       <c r="D29" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A29,Sheet1!$B$3:$B$53,0),MATCH(B29,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.890567115157197</v>
+        <f aca="false">IF(AND($A29="",$B29=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A29,Sheet1!$B$3:$B$53,0),MATCH($B29,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.550544014823825</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2360,8 +2360,8 @@
         <v>57</v>
       </c>
       <c r="D30" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A30,Sheet1!$B$3:$B$53,0),MATCH(B30,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.202300147891679</v>
+        <f aca="false">IF(AND($A30="",$B30=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A30,Sheet1!$B$3:$B$53,0),MATCH($B30,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.890567115157197</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2375,8 +2375,8 @@
         <v>57</v>
       </c>
       <c r="D31" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A31,Sheet1!$B$3:$B$53,0),MATCH(B31,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.00735575830023227</v>
+        <f aca="false">IF(AND($A31="",$B31=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A31,Sheet1!$B$3:$B$53,0),MATCH($B31,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.202300147891679</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2390,8 +2390,8 @@
         <v>57</v>
       </c>
       <c r="D32" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A32,Sheet1!$B$3:$B$53,0),MATCH(B32,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.496075380477184</v>
+        <f aca="false">IF(AND($A32="",$B32=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A32,Sheet1!$B$3:$B$53,0),MATCH($B32,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.00735575830023227</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2405,8 +2405,8 @@
         <v>57</v>
       </c>
       <c r="D33" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A33,Sheet1!$B$3:$B$53,0),MATCH(B33,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.558832213932223</v>
+        <f aca="false">IF(AND($A33="",$B33=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A33,Sheet1!$B$3:$B$53,0),MATCH($B33,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.496075380477184</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2420,8 +2420,8 @@
         <v>57</v>
       </c>
       <c r="D34" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A34,Sheet1!$B$3:$B$53,0),MATCH(B34,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.0428436978656417</v>
+        <f aca="false">IF(AND($A34="",$B34=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A34,Sheet1!$B$3:$B$53,0),MATCH($B34,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.558832213932223</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2435,8 +2435,8 @@
         <v>57</v>
       </c>
       <c r="D35" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A35,Sheet1!$B$3:$B$53,0),MATCH(B35,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.882410020278209</v>
+        <f aca="false">IF(AND($A35="",$B35=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A35,Sheet1!$B$3:$B$53,0),MATCH($B35,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.0428436978656417</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2450,8 +2450,8 @@
         <v>57</v>
       </c>
       <c r="D36" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A36,Sheet1!$B$3:$B$53,0),MATCH(B36,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.310705510900574</v>
+        <f aca="false">IF(AND($A36="",$B36=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A36,Sheet1!$B$3:$B$53,0),MATCH($B36,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.882410020278209</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2465,8 +2465,8 @@
         <v>57</v>
       </c>
       <c r="D37" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A37,Sheet1!$B$3:$B$53,0),MATCH(B37,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.439263017872823</v>
+        <f aca="false">IF(AND($A37="",$B37=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A37,Sheet1!$B$3:$B$53,0),MATCH($B37,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.310705510900574</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2480,8 +2480,8 @@
         <v>57</v>
       </c>
       <c r="D38" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A38,Sheet1!$B$3:$B$53,0),MATCH(B38,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.0273297160175079</v>
+        <f aca="false">IF(AND($A38="",$B38=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A38,Sheet1!$B$3:$B$53,0),MATCH($B38,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.439263017872823</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2495,8 +2495,8 @@
         <v>57</v>
       </c>
       <c r="D39" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A39,Sheet1!$B$3:$B$53,0),MATCH(B39,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.0501955902408249</v>
+        <f aca="false">IF(AND($A39="",$B39=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A39,Sheet1!$B$3:$B$53,0),MATCH($B39,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.0273297160175079</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2510,8 +2510,8 @@
         <v>57</v>
       </c>
       <c r="D40" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A40,Sheet1!$B$3:$B$53,0),MATCH(B40,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.273687996920313</v>
+        <f aca="false">IF(AND($A40="",$B40=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A40,Sheet1!$B$3:$B$53,0),MATCH($B40,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.0501955902408249</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2525,8 +2525,8 @@
         <v>57</v>
       </c>
       <c r="D41" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A41,Sheet1!$B$3:$B$53,0),MATCH(B41,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.553405555572344</v>
+        <f aca="false">IF(AND($A41="",$B41=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A41,Sheet1!$B$3:$B$53,0),MATCH($B41,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.273687996920313</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2540,8 +2540,8 @@
         <v>57</v>
       </c>
       <c r="D42" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A42,Sheet1!$B$3:$B$53,0),MATCH(B42,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.710532187831164</v>
+        <f aca="false">IF(AND($A42="",$B42=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A42,Sheet1!$B$3:$B$53,0),MATCH($B42,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.553405555572344</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2555,8 +2555,8 @@
         <v>57</v>
       </c>
       <c r="D43" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A43,Sheet1!$B$3:$B$53,0),MATCH(B43,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.600354862054731</v>
+        <f aca="false">IF(AND($A43="",$B43=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A43,Sheet1!$B$3:$B$53,0),MATCH($B43,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.710532187831164</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2570,8 +2570,8 @@
         <v>57</v>
       </c>
       <c r="D44" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A44,Sheet1!$B$3:$B$53,0),MATCH(B44,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.917780517589332</v>
+        <f aca="false">IF(AND($A44="",$B44=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A44,Sheet1!$B$3:$B$53,0),MATCH($B44,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.600354862054731</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2585,8 +2585,8 @@
         <v>57</v>
       </c>
       <c r="D45" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A45,Sheet1!$B$3:$B$53,0),MATCH(B45,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.986746239438198</v>
+        <f aca="false">IF(AND($A45="",$B45=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A45,Sheet1!$B$3:$B$53,0),MATCH($B45,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.917780517589332</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2600,8 +2600,8 @@
         <v>57</v>
       </c>
       <c r="D46" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A46,Sheet1!$B$3:$B$53,0),MATCH(B46,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.993736391918462</v>
+        <f aca="false">IF(AND($A46="",$B46=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A46,Sheet1!$B$3:$B$53,0),MATCH($B46,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.986746239438198</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2615,8 +2615,8 @@
         <v>57</v>
       </c>
       <c r="D47" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A47,Sheet1!$B$3:$B$53,0),MATCH(B47,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.866009327847726</v>
+        <f aca="false">IF(AND($A47="",$B47=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A47,Sheet1!$B$3:$B$53,0),MATCH($B47,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.993736391918462</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2630,8 +2630,8 @@
         <v>57</v>
       </c>
       <c r="D48" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A48,Sheet1!$B$3:$B$53,0),MATCH(B48,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.587973316119502</v>
+        <f aca="false">IF(AND($A48="",$B48=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A48,Sheet1!$B$3:$B$53,0),MATCH($B48,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.866009327847726</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2645,8 +2645,8 @@
         <v>57</v>
       </c>
       <c r="D49" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A49,Sheet1!$B$3:$B$53,0),MATCH(B49,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.580041001463718</v>
+        <f aca="false">IF(AND($A49="",$B49=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A49,Sheet1!$B$3:$B$53,0),MATCH($B49,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.587973316119502</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2660,8 +2660,8 @@
         <v>57</v>
       </c>
       <c r="D50" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A50,Sheet1!$B$3:$B$53,0),MATCH(B50,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.018459623561665</v>
+        <f aca="false">IF(AND($A50="",$B50=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A50,Sheet1!$B$3:$B$53,0),MATCH($B50,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.580041001463718</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2675,8 +2675,8 @@
         <v>57</v>
       </c>
       <c r="D51" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A51,Sheet1!$B$3:$B$53,0),MATCH(B51,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.214511253668006</v>
+        <f aca="false">IF(AND($A51="",$B51=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A51,Sheet1!$B$3:$B$53,0),MATCH($B51,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.018459623561665</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2690,8 +2690,8 @@
         <v>57</v>
       </c>
       <c r="D52" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A52,Sheet1!$B$3:$B$53,0),MATCH(B52,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.299133276706589</v>
+        <f aca="false">IF(AND($A52="",$B52=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A52,Sheet1!$B$3:$B$53,0),MATCH($B52,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.214511253668006</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2705,8 +2705,8 @@
         <v>57</v>
       </c>
       <c r="D53" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A53,Sheet1!$B$3:$B$53,0),MATCH(B53,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.044715484600623</v>
+        <f aca="false">IF(AND($A53="",$B53=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A53,Sheet1!$B$3:$B$53,0),MATCH($B53,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.299133276706589</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2720,8 +2720,8 @@
         <v>57</v>
       </c>
       <c r="D54" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A54,Sheet1!$B$3:$B$53,0),MATCH(B54,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.369694550249851</v>
+        <f aca="false">IF(AND($A54="",$B54=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A54,Sheet1!$B$3:$B$53,0),MATCH($B54,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2735,8 +2735,8 @@
         <v>57</v>
       </c>
       <c r="D55" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A55,Sheet1!$B$3:$B$53,0),MATCH(B55,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.718165777391587</v>
+        <f aca="false">IF(AND($A55="",$B55=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A55,Sheet1!$B$3:$B$53,0),MATCH($B55,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.369694550249851</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2750,8 +2750,8 @@
         <v>57</v>
       </c>
       <c r="D56" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A56,Sheet1!$B$3:$B$53,0),MATCH(B56,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.647574861591199</v>
+        <f aca="false">IF(AND($A56="",$B56=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A56,Sheet1!$B$3:$B$53,0),MATCH($B56,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.718165777391587</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2765,8 +2765,8 @@
         <v>57</v>
       </c>
       <c r="D57" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A57,Sheet1!$B$3:$B$53,0),MATCH(B57,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.918250677089609</v>
+        <f aca="false">IF(AND($A57="",$B57=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A57,Sheet1!$B$3:$B$53,0),MATCH($B57,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.647574861591199</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2780,8 +2780,8 @@
         <v>57</v>
       </c>
       <c r="D58" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A58,Sheet1!$B$3:$B$53,0),MATCH(B58,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.470295046817084</v>
+        <f aca="false">IF(AND($A58="",$B58=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A58,Sheet1!$B$3:$B$53,0),MATCH($B58,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.918250677089609</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2795,8 +2795,8 @@
         <v>57</v>
       </c>
       <c r="D59" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A59,Sheet1!$B$3:$B$53,0),MATCH(B59,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.56978655216477</v>
+        <f aca="false">IF(AND($A59="",$B59=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A59,Sheet1!$B$3:$B$53,0),MATCH($B59,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.470295046817084</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2810,8 +2810,8 @@
         <v>57</v>
       </c>
       <c r="D60" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A60,Sheet1!$B$3:$B$53,0),MATCH(B60,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.314761212646374</v>
+        <f aca="false">IF(AND($A60="",$B60=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A60,Sheet1!$B$3:$B$53,0),MATCH($B60,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.56978655216477</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2825,8 +2825,8 @@
         <v>57</v>
       </c>
       <c r="D61" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A61,Sheet1!$B$3:$B$53,0),MATCH(B61,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.619263449452447</v>
+        <f aca="false">IF(AND($A61="",$B61=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A61,Sheet1!$B$3:$B$53,0),MATCH($B61,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.314761212646374</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2840,8 +2840,8 @@
         <v>57</v>
       </c>
       <c r="D62" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A62,Sheet1!$B$3:$B$53,0),MATCH(B62,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.422234596278344</v>
+        <f aca="false">IF(AND($A62="",$B62=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A62,Sheet1!$B$3:$B$53,0),MATCH($B62,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.619263449452447</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2855,8 +2855,8 @@
         <v>57</v>
       </c>
       <c r="D63" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A63,Sheet1!$B$3:$B$53,0),MATCH(B63,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.110630909969275</v>
+        <f aca="false">IF(AND($A63="",$B63=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A63,Sheet1!$B$3:$B$53,0),MATCH($B63,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.422234596278344</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2870,8 +2870,8 @@
         <v>57</v>
       </c>
       <c r="D64" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A64,Sheet1!$B$3:$B$53,0),MATCH(B64,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.504589039555236</v>
+        <f aca="false">IF(AND($A64="",$B64=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A64,Sheet1!$B$3:$B$53,0),MATCH($B64,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.110630909969275</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2885,8 +2885,8 @@
         <v>57</v>
       </c>
       <c r="D65" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A65,Sheet1!$B$3:$B$53,0),MATCH(B65,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.561936675559634</v>
+        <f aca="false">IF(AND($A65="",$B65=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A65,Sheet1!$B$3:$B$53,0),MATCH($B65,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.504589039555236</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2900,8 +2900,8 @@
         <v>57</v>
       </c>
       <c r="D66" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A66,Sheet1!$B$3:$B$53,0),MATCH(B66,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.0121997857164132</v>
+        <f aca="false">IF(AND($A66="",$B66=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A66,Sheet1!$B$3:$B$53,0),MATCH($B66,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.561936675559634</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2915,8 +2915,8 @@
         <v>57</v>
       </c>
       <c r="D67" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A67,Sheet1!$B$3:$B$53,0),MATCH(B67,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.0744918816064607</v>
+        <f aca="false">IF(AND($A67="",$B67=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A67,Sheet1!$B$3:$B$53,0),MATCH($B67,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.0121997857164132</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2930,8 +2930,8 @@
         <v>57</v>
       </c>
       <c r="D68" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A68,Sheet1!$B$3:$B$53,0),MATCH(B68,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.101270170745148</v>
+        <f aca="false">IF(AND($A68="",$B68=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A68,Sheet1!$B$3:$B$53,0),MATCH($B68,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.0744918816064607</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2945,8 +2945,8 @@
         <v>57</v>
       </c>
       <c r="D69" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A69,Sheet1!$B$3:$B$53,0),MATCH(B69,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.444939584993711</v>
+        <f aca="false">IF(AND($A69="",$B69=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A69,Sheet1!$B$3:$B$53,0),MATCH($B69,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.101270170745148</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2960,8 +2960,8 @@
         <v>57</v>
       </c>
       <c r="D70" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A70,Sheet1!$B$3:$B$53,0),MATCH(B70,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.813128951408209</v>
+        <f aca="false">IF(AND($A70="",$B70=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A70,Sheet1!$B$3:$B$53,0),MATCH($B70,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.444939584993711</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2975,8 +2975,8 @@
         <v>57</v>
       </c>
       <c r="D71" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A71,Sheet1!$B$3:$B$53,0),MATCH(B71,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.833368049338167</v>
+        <f aca="false">IF(AND($A71="",$B71=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A71,Sheet1!$B$3:$B$53,0),MATCH($B71,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.813128951408209</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2990,8 +2990,8 @@
         <v>57</v>
       </c>
       <c r="D72" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A72,Sheet1!$B$3:$B$53,0),MATCH(B72,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.980309702492869</v>
+        <f aca="false">IF(AND($A72="",$B72=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A72,Sheet1!$B$3:$B$53,0),MATCH($B72,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.833368049338167</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3005,8 +3005,8 @@
         <v>57</v>
       </c>
       <c r="D73" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A73,Sheet1!$B$3:$B$53,0),MATCH(B73,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.167787479706479</v>
+        <f aca="false">IF(AND($A73="",$B73=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A73,Sheet1!$B$3:$B$53,0),MATCH($B73,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.980309702492869</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3020,8 +3020,8 @@
         <v>57</v>
       </c>
       <c r="D74" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A74,Sheet1!$B$3:$B$53,0),MATCH(B74,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.745094760504618</v>
+        <f aca="false">IF(AND($A74="",$B74=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A74,Sheet1!$B$3:$B$53,0),MATCH($B74,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.167787479706479</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3035,8 +3035,8 @@
         <v>57</v>
       </c>
       <c r="D75" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A75,Sheet1!$B$3:$B$53,0),MATCH(B75,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.392068209481472</v>
+        <f aca="false">IF(AND($A75="",$B75=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A75,Sheet1!$B$3:$B$53,0),MATCH($B75,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.745094760504618</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3050,8 +3050,8 @@
         <v>57</v>
       </c>
       <c r="D76" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A76,Sheet1!$B$3:$B$53,0),MATCH(B76,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.404066649594268</v>
+        <f aca="false">IF(AND($A76="",$B76=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A76,Sheet1!$B$3:$B$53,0),MATCH($B76,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.392068209481472</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3065,8 +3065,8 @@
         <v>57</v>
       </c>
       <c r="D77" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A77,Sheet1!$B$3:$B$53,0),MATCH(B77,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.962098177585588</v>
+        <f aca="false">IF(AND($A77="",$B77=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A77,Sheet1!$B$3:$B$53,0),MATCH($B77,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.404066649594268</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3080,8 +3080,8 @@
         <v>57</v>
       </c>
       <c r="D78" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A78,Sheet1!$B$3:$B$53,0),MATCH(B78,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.0463131954792417</v>
+        <f aca="false">IF(AND($A78="",$B78=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A78,Sheet1!$B$3:$B$53,0),MATCH($B78,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.962098177585588</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3095,8 +3095,8 @@
         <v>57</v>
       </c>
       <c r="D79" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A79,Sheet1!$B$3:$B$53,0),MATCH(B79,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.987397660151677</v>
+        <f aca="false">IF(AND($A79="",$B79=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A79,Sheet1!$B$3:$B$53,0),MATCH($B79,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.0463131954792417</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3110,8 +3110,8 @@
         <v>57</v>
       </c>
       <c r="D80" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A80,Sheet1!$B$3:$B$53,0),MATCH(B80,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.434370975072386</v>
+        <f aca="false">IF(AND($A80="",$B80=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A80,Sheet1!$B$3:$B$53,0),MATCH($B80,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.987397660151677</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3125,8 +3125,8 @@
         <v>57</v>
       </c>
       <c r="D81" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A81,Sheet1!$B$3:$B$53,0),MATCH(B81,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.778758181214608</v>
+        <f aca="false">IF(AND($A81="",$B81=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A81,Sheet1!$B$3:$B$53,0),MATCH($B81,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.434370975072386</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3140,8 +3140,8 @@
         <v>57</v>
       </c>
       <c r="D82" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A82,Sheet1!$B$3:$B$53,0),MATCH(B82,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.997040199373517</v>
+        <f aca="false">IF(AND($A82="",$B82=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A82,Sheet1!$B$3:$B$53,0),MATCH($B82,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.778758181214608</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3155,8 +3155,8 @@
         <v>57</v>
       </c>
       <c r="D83" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A83,Sheet1!$B$3:$B$53,0),MATCH(B83,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.546003573654997</v>
+        <f aca="false">IF(AND($A83="",$B83=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A83,Sheet1!$B$3:$B$53,0),MATCH($B83,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.997040199373517</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3170,8 +3170,8 @@
         <v>57</v>
       </c>
       <c r="D84" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A84,Sheet1!$B$3:$B$53,0),MATCH(B84,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.0958252934572622</v>
+        <f aca="false">IF(AND($A84="",$B84=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A84,Sheet1!$B$3:$B$53,0),MATCH($B84,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.546003573654997</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3185,8 +3185,8 @@
         <v>57</v>
       </c>
       <c r="D85" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A85,Sheet1!$B$3:$B$53,0),MATCH(B85,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.165230235461094</v>
+        <f aca="false">IF(AND($A85="",$B85=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A85,Sheet1!$B$3:$B$53,0),MATCH($B85,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.0958252934572622</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3200,8 +3200,8 @@
         <v>57</v>
       </c>
       <c r="D86" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A86,Sheet1!$B$3:$B$53,0),MATCH(B86,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.607227175985319</v>
+        <f aca="false">IF(AND($A86="",$B86=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A86,Sheet1!$B$3:$B$53,0),MATCH($B86,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.165230235461094</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3215,8 +3215,8 @@
         <v>57</v>
       </c>
       <c r="D87" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A87,Sheet1!$B$3:$B$53,0),MATCH(B87,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.615480699777199</v>
+        <f aca="false">IF(AND($A87="",$B87=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A87,Sheet1!$B$3:$B$53,0),MATCH($B87,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.607227175985319</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3230,8 +3230,8 @@
         <v>57</v>
       </c>
       <c r="D88" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A88,Sheet1!$B$3:$B$53,0),MATCH(B88,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.0752928224532246</v>
+        <f aca="false">IF(AND($A88="",$B88=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A88,Sheet1!$B$3:$B$53,0),MATCH($B88,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.615480699777199</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3245,8 +3245,8 @@
         <v>57</v>
       </c>
       <c r="D89" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A89,Sheet1!$B$3:$B$53,0),MATCH(B89,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.610100540542761</v>
+        <f aca="false">IF(AND($A89="",$B89=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A89,Sheet1!$B$3:$B$53,0),MATCH($B89,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.0752928224532246</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3260,8 +3260,8 @@
         <v>57</v>
       </c>
       <c r="D90" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A90,Sheet1!$B$3:$B$53,0),MATCH(B90,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.763686911335516</v>
+        <f aca="false">IF(AND($A90="",$B90=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A90,Sheet1!$B$3:$B$53,0),MATCH($B90,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.610100540542761</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3275,8 +3275,8 @@
         <v>57</v>
       </c>
       <c r="D91" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A91,Sheet1!$B$3:$B$53,0),MATCH(B91,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.636128995056395</v>
+        <f aca="false">IF(AND($A91="",$B91=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A91,Sheet1!$B$3:$B$53,0),MATCH($B91,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.763686911335516</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3290,8 +3290,8 @@
         <v>57</v>
       </c>
       <c r="D92" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A92,Sheet1!$B$3:$B$53,0),MATCH(B92,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.575857431069105</v>
+        <f aca="false">IF(AND($A92="",$B92=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A92,Sheet1!$B$3:$B$53,0),MATCH($B92,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.636128995056395</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3305,8 +3305,8 @@
         <v>57</v>
       </c>
       <c r="D93" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A93,Sheet1!$B$3:$B$53,0),MATCH(B93,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.343891426227658</v>
+        <f aca="false">IF(AND($A93="",$B93=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A93,Sheet1!$B$3:$B$53,0),MATCH($B93,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.575857431069105</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3320,8 +3320,8 @@
         <v>57</v>
       </c>
       <c r="D94" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A94,Sheet1!$B$3:$B$53,0),MATCH(B94,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.653806671834964</v>
+        <f aca="false">IF(AND($A94="",$B94=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A94,Sheet1!$B$3:$B$53,0),MATCH($B94,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.343891426227658</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3335,8 +3335,8 @@
         <v>57</v>
       </c>
       <c r="D95" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A95,Sheet1!$B$3:$B$53,0),MATCH(B95,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.149385919903291</v>
+        <f aca="false">IF(AND($A95="",$B95=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A95,Sheet1!$B$3:$B$53,0),MATCH($B95,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.653806671834964</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3350,8 +3350,8 @@
         <v>57</v>
       </c>
       <c r="D96" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A96,Sheet1!$B$3:$B$53,0),MATCH(B96,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.527954419892915</v>
+        <f aca="false">IF(AND($A96="",$B96=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A96,Sheet1!$B$3:$B$53,0),MATCH($B96,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.149385919903291</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3365,8 +3365,8 @@
         <v>57</v>
       </c>
       <c r="D97" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A97,Sheet1!$B$3:$B$53,0),MATCH(B97,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.2755163089957</v>
+        <f aca="false">IF(AND($A97="",$B97=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A97,Sheet1!$B$3:$B$53,0),MATCH($B97,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.527954419892915</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3380,8 +3380,8 @@
         <v>57</v>
       </c>
       <c r="D98" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A98,Sheet1!$B$3:$B$53,0),MATCH(B98,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.992256787142238</v>
+        <f aca="false">IF(AND($A98="",$B98=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A98,Sheet1!$B$3:$B$53,0),MATCH($B98,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.2755163089957</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3395,8 +3395,8 @@
         <v>57</v>
       </c>
       <c r="D99" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A99,Sheet1!$B$3:$B$53,0),MATCH(B99,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.142677548392102</v>
+        <f aca="false">IF(AND($A99="",$B99=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A99,Sheet1!$B$3:$B$53,0),MATCH($B99,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.992256787142238</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3410,8 +3410,8 @@
         <v>57</v>
       </c>
       <c r="D100" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A100,Sheet1!$B$3:$B$53,0),MATCH(B100,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.840555762180691</v>
+        <f aca="false">IF(AND($A100="",$B100=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A100,Sheet1!$B$3:$B$53,0),MATCH($B100,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.142677548392102</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3425,8 +3425,8 @@
         <v>57</v>
       </c>
       <c r="D101" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A101,Sheet1!$B$3:$B$53,0),MATCH(B101,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.362233557798657</v>
+        <f aca="false">IF(AND($A101="",$B101=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A101,Sheet1!$B$3:$B$53,0),MATCH($B101,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.840555762180691</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3440,8 +3440,8 @@
         <v>57</v>
       </c>
       <c r="D102" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A102,Sheet1!$B$3:$B$53,0),MATCH(B102,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.441236679934384</v>
+        <f aca="false">IF(AND($A102="",$B102=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A102,Sheet1!$B$3:$B$53,0),MATCH($B102,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.362233557798657</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3455,8 +3455,8 @@
         <v>57</v>
       </c>
       <c r="D103" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A103,Sheet1!$B$3:$B$53,0),MATCH(B103,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.972255814663594</v>
+        <f aca="false">IF(AND($A103="",$B103=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A103,Sheet1!$B$3:$B$53,0),MATCH($B103,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.441236679934384</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3470,8 +3470,8 @@
         <v>57</v>
       </c>
       <c r="D104" s="1" t="n">
-        <f aca="false">INDEX(Sheet1!$L$3:$R$53,MATCH(A104,Sheet1!$B$3:$B$53,0),MATCH(B104,Sheet1!$L$1:$R$1,0))</f>
-        <v>0.556747538399581</v>
+        <f aca="false">IF(AND($A104="",$B104=""),"",INDEX(Sheet1!$K$2:$R$53,MATCH($A104,Sheet1!$B$3:$B$53,0),MATCH($B104,Sheet1!$K$1:$R$1,0)))</f>
+        <v>0.972255814663594</v>
       </c>
     </row>
   </sheetData>
